--- a/compare/output/dscale_RenTES_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_RenTES_downscaled_SSP245.xlsx
@@ -526,58 +526,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>452247.473105</v>
+        <v>452155.822629</v>
       </c>
       <c r="F2" t="n">
-        <v>466296.331589</v>
+        <v>466114.764208</v>
       </c>
       <c r="G2" t="n">
-        <v>544609.2113889999</v>
+        <v>544299.657982</v>
       </c>
       <c r="H2" t="n">
-        <v>648026.10237</v>
+        <v>647544.645915</v>
       </c>
       <c r="I2" t="n">
-        <v>766606.213806</v>
+        <v>765904.746616</v>
       </c>
       <c r="J2" t="n">
-        <v>938804.605509</v>
+        <v>937785.703861</v>
       </c>
       <c r="K2" t="n">
-        <v>1157481.649958</v>
+        <v>1156026.965639</v>
       </c>
       <c r="L2" t="n">
-        <v>1371795.207532</v>
+        <v>1369831.136153</v>
       </c>
       <c r="M2" t="n">
-        <v>1633812.622607</v>
+        <v>1631174.49516</v>
       </c>
       <c r="N2" t="n">
-        <v>1957419.537917</v>
+        <v>1953875.12991</v>
       </c>
       <c r="O2" t="n">
-        <v>2338088.000674</v>
+        <v>2333351.905831</v>
       </c>
       <c r="P2" t="n">
-        <v>2731715.085334</v>
+        <v>2725525.324376</v>
       </c>
       <c r="Q2" t="n">
-        <v>3127443.138333</v>
+        <v>3119492.962592</v>
       </c>
       <c r="R2" t="n">
-        <v>3497257.939179</v>
+        <v>3487219.668647</v>
       </c>
       <c r="S2" t="n">
-        <v>3847722.112356</v>
+        <v>3835121.329606</v>
       </c>
       <c r="T2" t="n">
-        <v>4156105.29282</v>
+        <v>4140326.125508</v>
       </c>
       <c r="U2" t="n">
-        <v>4461216.519044</v>
+        <v>4441155.941087</v>
       </c>
       <c r="V2" t="n">
-        <v>4729347.420373</v>
+        <v>4703340.639832</v>
       </c>
     </row>
     <row r="3">
@@ -602,58 +602,58 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38551.326906</v>
+        <v>38544.354454</v>
       </c>
       <c r="F3" t="n">
-        <v>35583.055062</v>
+        <v>35570.863207</v>
       </c>
       <c r="G3" t="n">
-        <v>38992.803247</v>
+        <v>38973.426014</v>
       </c>
       <c r="H3" t="n">
-        <v>45351.978422</v>
+        <v>45322.589358</v>
       </c>
       <c r="I3" t="n">
-        <v>54159.28668</v>
+        <v>54116.017706</v>
       </c>
       <c r="J3" t="n">
-        <v>69037.20149000001</v>
+        <v>68971.404674</v>
       </c>
       <c r="K3" t="n">
-        <v>90636.24153299999</v>
+        <v>90535.16938599999</v>
       </c>
       <c r="L3" t="n">
-        <v>114133.372266</v>
+        <v>113986.747332</v>
       </c>
       <c r="M3" t="n">
-        <v>141818.03622</v>
+        <v>141610.738081</v>
       </c>
       <c r="N3" t="n">
-        <v>172597.226927</v>
+        <v>172312.925266</v>
       </c>
       <c r="O3" t="n">
-        <v>204817.99041</v>
+        <v>204440.140671</v>
       </c>
       <c r="P3" t="n">
-        <v>234281.221374</v>
+        <v>233798.321253</v>
       </c>
       <c r="Q3" t="n">
-        <v>261115.967187</v>
+        <v>260513.471899</v>
       </c>
       <c r="R3" t="n">
-        <v>284478.213672</v>
+        <v>283738.80442</v>
       </c>
       <c r="S3" t="n">
-        <v>309990.882316</v>
+        <v>309071.646765</v>
       </c>
       <c r="T3" t="n">
-        <v>333422.33232</v>
+        <v>332275.424908</v>
       </c>
       <c r="U3" t="n">
-        <v>354495.149029</v>
+        <v>353051.99896</v>
       </c>
       <c r="V3" t="n">
-        <v>368225.572389</v>
+        <v>366398.644258</v>
       </c>
     </row>
     <row r="4">
@@ -678,58 +678,58 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45419.641408</v>
+        <v>45412.834313</v>
       </c>
       <c r="F4" t="n">
-        <v>37105.834808</v>
+        <v>37095.787285</v>
       </c>
       <c r="G4" t="n">
-        <v>35033.131984</v>
+        <v>35020.130434</v>
       </c>
       <c r="H4" t="n">
-        <v>36497.802311</v>
+        <v>36480.893913</v>
       </c>
       <c r="I4" t="n">
-        <v>40219.509122</v>
+        <v>40197.228674</v>
       </c>
       <c r="J4" t="n">
-        <v>47556.461784</v>
+        <v>47525.808873</v>
       </c>
       <c r="K4" t="n">
-        <v>57577.519509</v>
+        <v>57535.095879</v>
       </c>
       <c r="L4" t="n">
-        <v>66802.596945</v>
+        <v>66747.137327</v>
       </c>
       <c r="M4" t="n">
-        <v>76875.589139</v>
+        <v>76804.40379900001</v>
       </c>
       <c r="N4" t="n">
-        <v>87730.788721</v>
+        <v>87640.75300500001</v>
       </c>
       <c r="O4" t="n">
-        <v>99255.340992</v>
+        <v>99142.61844400001</v>
       </c>
       <c r="P4" t="n">
-        <v>109812.718912</v>
+        <v>109674.550684</v>
       </c>
       <c r="Q4" t="n">
-        <v>119406.830821</v>
+        <v>119239.777779</v>
       </c>
       <c r="R4" t="n">
-        <v>127334.843526</v>
+        <v>127135.445979</v>
       </c>
       <c r="S4" t="n">
-        <v>134061.085547</v>
+        <v>133823.738832</v>
       </c>
       <c r="T4" t="n">
-        <v>138596.57241</v>
+        <v>138314.893217</v>
       </c>
       <c r="U4" t="n">
-        <v>142259.107854</v>
+        <v>141921.196591</v>
       </c>
       <c r="V4" t="n">
-        <v>144508.159501</v>
+        <v>144096.311133</v>
       </c>
     </row>
     <row r="5">
@@ -754,58 +754,58 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21708.690764</v>
+        <v>21718.054515</v>
       </c>
       <c r="F5" t="n">
-        <v>26208.205251</v>
+        <v>26227.593469</v>
       </c>
       <c r="G5" t="n">
-        <v>38817.860447</v>
+        <v>38852.176899</v>
       </c>
       <c r="H5" t="n">
-        <v>56214.669169</v>
+        <v>56270.215719</v>
       </c>
       <c r="I5" t="n">
-        <v>76352.479179</v>
+        <v>76437.534833</v>
       </c>
       <c r="J5" t="n">
-        <v>102131.565557</v>
+        <v>102262.456232</v>
       </c>
       <c r="K5" t="n">
-        <v>133257.385691</v>
+        <v>133454.790517</v>
       </c>
       <c r="L5" t="n">
-        <v>163296.444768</v>
+        <v>163573.630436</v>
       </c>
       <c r="M5" t="n">
-        <v>196764.537013</v>
+        <v>197143.598032</v>
       </c>
       <c r="N5" t="n">
-        <v>233881.827204</v>
+        <v>234389.8051</v>
       </c>
       <c r="O5" t="n">
-        <v>273630.27233</v>
+        <v>274298.276426</v>
       </c>
       <c r="P5" t="n">
-        <v>310718.211439</v>
+        <v>311572.016965</v>
       </c>
       <c r="Q5" t="n">
-        <v>344826.913738</v>
+        <v>345897.210079</v>
       </c>
       <c r="R5" t="n">
-        <v>374719.290178</v>
+        <v>376039.286509</v>
       </c>
       <c r="S5" t="n">
-        <v>401901.401459</v>
+        <v>403519.037533</v>
       </c>
       <c r="T5" t="n">
-        <v>423636.8069</v>
+        <v>425609.719344</v>
       </c>
       <c r="U5" t="n">
-        <v>443366.096939</v>
+        <v>445810.859849</v>
       </c>
       <c r="V5" t="n">
-        <v>458809.460274</v>
+        <v>461916.255366</v>
       </c>
     </row>
     <row r="6">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1152679.409879</v>
+        <v>1152665.778958</v>
       </c>
       <c r="F6" t="n">
-        <v>1172988.67365</v>
+        <v>1172962.65854</v>
       </c>
       <c r="G6" t="n">
-        <v>1246406.79722</v>
+        <v>1246397.62297</v>
       </c>
       <c r="H6" t="n">
-        <v>1383140.105827</v>
+        <v>1383171.848355</v>
       </c>
       <c r="I6" t="n">
-        <v>1593851.448005</v>
+        <v>1593940.043523</v>
       </c>
       <c r="J6" t="n">
-        <v>1954210.8096</v>
+        <v>1954384.178091</v>
       </c>
       <c r="K6" t="n">
-        <v>2450971.678723</v>
+        <v>2451263.723394</v>
       </c>
       <c r="L6" t="n">
-        <v>2934440.994631</v>
+        <v>2934885.648211</v>
       </c>
       <c r="M6" t="n">
-        <v>3491288.995911</v>
+        <v>3491928.730766</v>
       </c>
       <c r="N6" t="n">
-        <v>4134489.012126</v>
+        <v>4135359.835416</v>
       </c>
       <c r="O6" t="n">
-        <v>4865066.697805</v>
+        <v>4866186.188068</v>
       </c>
       <c r="P6" t="n">
-        <v>5603090.715759</v>
+        <v>5604453.472372</v>
       </c>
       <c r="Q6" t="n">
-        <v>6349963.741998</v>
+        <v>6351556.894544</v>
       </c>
       <c r="R6" t="n">
-        <v>7040682.331196</v>
+        <v>7042512.824898</v>
       </c>
       <c r="S6" t="n">
-        <v>7664894.476578</v>
+        <v>7667035.691037</v>
       </c>
       <c r="T6" t="n">
-        <v>8146992.79094</v>
+        <v>8149559.431066</v>
       </c>
       <c r="U6" t="n">
-        <v>8570995.496982999</v>
+        <v>8574289.516496999</v>
       </c>
       <c r="V6" t="n">
-        <v>9073606.603559</v>
+        <v>9077707.225403</v>
       </c>
     </row>
     <row r="7">
@@ -906,58 +906,58 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>645211.78678</v>
+        <v>645217.900307</v>
       </c>
       <c r="F7" t="n">
-        <v>694281.7096140001</v>
+        <v>694285.706974</v>
       </c>
       <c r="G7" t="n">
-        <v>879089.52672</v>
+        <v>879068.222176</v>
       </c>
       <c r="H7" t="n">
-        <v>1148516.418257</v>
+        <v>1148438.637485</v>
       </c>
       <c r="I7" t="n">
-        <v>1498349.68127</v>
+        <v>1498172.771039</v>
       </c>
       <c r="J7" t="n">
-        <v>2010304.696535</v>
+        <v>2009962.808245</v>
       </c>
       <c r="K7" t="n">
-        <v>2675400.111114</v>
+        <v>2674808.246279</v>
       </c>
       <c r="L7" t="n">
-        <v>3321713.071592</v>
+        <v>3320827.567499</v>
       </c>
       <c r="M7" t="n">
-        <v>4005506.038134</v>
+        <v>4004287.814817</v>
       </c>
       <c r="N7" t="n">
-        <v>4710493.195734</v>
+        <v>4708928.718232</v>
       </c>
       <c r="O7" t="n">
-        <v>5412342.431962</v>
+        <v>5410448.742306</v>
       </c>
       <c r="P7" t="n">
-        <v>6009542.338593</v>
+        <v>6007393.192575</v>
       </c>
       <c r="Q7" t="n">
-        <v>6505685.024382</v>
+        <v>6503378.66597</v>
       </c>
       <c r="R7" t="n">
-        <v>6866453.670642</v>
+        <v>6864121.938781</v>
       </c>
       <c r="S7" t="n">
-        <v>7110378.566654</v>
+        <v>7108182.507094</v>
       </c>
       <c r="T7" t="n">
-        <v>7194284.837135</v>
+        <v>7192443.915455</v>
       </c>
       <c r="U7" t="n">
-        <v>7201165.751032</v>
+        <v>7200004.275332</v>
       </c>
       <c r="V7" t="n">
-        <v>7120283.440209</v>
+        <v>7120352.507552</v>
       </c>
     </row>
     <row r="8">
@@ -982,58 +982,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>189867.846968</v>
+        <v>189885.784916</v>
       </c>
       <c r="F8" t="n">
-        <v>192684.939737</v>
+        <v>192721.287185</v>
       </c>
       <c r="G8" t="n">
-        <v>225245.628931</v>
+        <v>225307.177823</v>
       </c>
       <c r="H8" t="n">
-        <v>272951.280491</v>
+        <v>273049.167754</v>
       </c>
       <c r="I8" t="n">
-        <v>333006.032645</v>
+        <v>333155.454206</v>
       </c>
       <c r="J8" t="n">
-        <v>421706.75439</v>
+        <v>421938.342266</v>
       </c>
       <c r="K8" t="n">
-        <v>535523.727253</v>
+        <v>535877.329832</v>
       </c>
       <c r="L8" t="n">
-        <v>644836.952142</v>
+        <v>645340.852796</v>
       </c>
       <c r="M8" t="n">
-        <v>764982.216232</v>
+        <v>765683.6174540001</v>
       </c>
       <c r="N8" t="n">
-        <v>895159.272361</v>
+        <v>896116.418618</v>
       </c>
       <c r="O8" t="n">
-        <v>1032500.537084</v>
+        <v>1033780.886621</v>
       </c>
       <c r="P8" t="n">
-        <v>1162709.914591</v>
+        <v>1164371.51111</v>
       </c>
       <c r="Q8" t="n">
-        <v>1289495.011504</v>
+        <v>1291608.51899</v>
       </c>
       <c r="R8" t="n">
-        <v>1407831.005092</v>
+        <v>1410468.629901</v>
       </c>
       <c r="S8" t="n">
-        <v>1521367.726372</v>
+        <v>1524633.288055</v>
       </c>
       <c r="T8" t="n">
-        <v>1618320.568982</v>
+        <v>1622335.682583</v>
       </c>
       <c r="U8" t="n">
-        <v>1713671.842488</v>
+        <v>1718694.9955</v>
       </c>
       <c r="V8" t="n">
-        <v>1801775.714887</v>
+        <v>1808237.200122</v>
       </c>
     </row>
     <row r="9">
@@ -1058,58 +1058,58 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8170.989464</v>
+        <v>8182.291767</v>
       </c>
       <c r="F9" t="n">
-        <v>6550.47772</v>
+        <v>6569.42998</v>
       </c>
       <c r="G9" t="n">
-        <v>5918.519295</v>
+        <v>5945.727209</v>
       </c>
       <c r="H9" t="n">
-        <v>5817.887663</v>
+        <v>5855.217704</v>
       </c>
       <c r="I9" t="n">
-        <v>6073.936498</v>
+        <v>6124.105706</v>
       </c>
       <c r="J9" t="n">
-        <v>6916.991507</v>
+        <v>6986.521136</v>
       </c>
       <c r="K9" t="n">
-        <v>8148.577245</v>
+        <v>8244.802107</v>
       </c>
       <c r="L9" t="n">
-        <v>9278.154193</v>
+        <v>9403.830376</v>
       </c>
       <c r="M9" t="n">
-        <v>10499.341554</v>
+        <v>10660.336909</v>
       </c>
       <c r="N9" t="n">
-        <v>11775.898389</v>
+        <v>11978.817116</v>
       </c>
       <c r="O9" t="n">
-        <v>13067.859504</v>
+        <v>13319.736509</v>
       </c>
       <c r="P9" t="n">
-        <v>14158.989809</v>
+        <v>14463.752575</v>
       </c>
       <c r="Q9" t="n">
-        <v>15111.055416</v>
+        <v>15474.446168</v>
       </c>
       <c r="R9" t="n">
-        <v>15862.823143</v>
+        <v>16290.646369</v>
       </c>
       <c r="S9" t="n">
-        <v>16439.675265</v>
+        <v>16941.189085</v>
       </c>
       <c r="T9" t="n">
-        <v>17129.228014</v>
+        <v>17721.201997</v>
       </c>
       <c r="U9" t="n">
-        <v>18096.968187</v>
+        <v>18812.143617</v>
       </c>
       <c r="V9" t="n">
-        <v>19308.089722</v>
+        <v>20196.956565</v>
       </c>
     </row>
     <row r="10">
@@ -1134,58 +1134,58 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>120533.986713</v>
+        <v>120544.992799</v>
       </c>
       <c r="F10" t="n">
-        <v>112410.612981</v>
+        <v>112434.075647</v>
       </c>
       <c r="G10" t="n">
-        <v>115281.099208</v>
+        <v>115322.987545</v>
       </c>
       <c r="H10" t="n">
-        <v>127281.754005</v>
+        <v>127349.809619</v>
       </c>
       <c r="I10" t="n">
-        <v>145886.221648</v>
+        <v>145991.094653</v>
       </c>
       <c r="J10" t="n">
-        <v>178805.23145</v>
+        <v>178967.798335</v>
       </c>
       <c r="K10" t="n">
-        <v>225448.899912</v>
+        <v>225695.856173</v>
       </c>
       <c r="L10" t="n">
-        <v>275003.661134</v>
+        <v>275352.594704</v>
       </c>
       <c r="M10" t="n">
-        <v>334746.71586</v>
+        <v>335225.310881</v>
       </c>
       <c r="N10" t="n">
-        <v>406359.275983</v>
+        <v>407001.044413</v>
       </c>
       <c r="O10" t="n">
-        <v>488416.006557</v>
+        <v>489261.860212</v>
       </c>
       <c r="P10" t="n">
-        <v>572235.091842</v>
+        <v>573320.906871</v>
       </c>
       <c r="Q10" t="n">
-        <v>656464.507092</v>
+        <v>657835.661803</v>
       </c>
       <c r="R10" t="n">
-        <v>738032.461418</v>
+        <v>739737.79339</v>
       </c>
       <c r="S10" t="n">
-        <v>819142.83128</v>
+        <v>821253.402133</v>
       </c>
       <c r="T10" t="n">
-        <v>893504.950294</v>
+        <v>896104.3573499999</v>
       </c>
       <c r="U10" t="n">
-        <v>967794.849493</v>
+        <v>971056.152636</v>
       </c>
       <c r="V10" t="n">
-        <v>1036329.66486</v>
+        <v>1040541.685519</v>
       </c>
     </row>
     <row r="11">
@@ -1210,58 +1210,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>384493.064386</v>
+        <v>384639.262881</v>
       </c>
       <c r="F11" t="n">
-        <v>381802.618098</v>
+        <v>382086.491843</v>
       </c>
       <c r="G11" t="n">
-        <v>436879.349643</v>
+        <v>437351.306887</v>
       </c>
       <c r="H11" t="n">
-        <v>527398.710017</v>
+        <v>528135.358962</v>
       </c>
       <c r="I11" t="n">
-        <v>643886.779269</v>
+        <v>644987.0145</v>
       </c>
       <c r="J11" t="n">
-        <v>809760.976276</v>
+        <v>811414.518011</v>
       </c>
       <c r="K11" t="n">
-        <v>1019381.579702</v>
+        <v>1021822.365487</v>
       </c>
       <c r="L11" t="n">
-        <v>1207526.518887</v>
+        <v>1210882.838931</v>
       </c>
       <c r="M11" t="n">
-        <v>1410217.04695</v>
+        <v>1414719.532107</v>
       </c>
       <c r="N11" t="n">
-        <v>1631556.042191</v>
+        <v>1637480.407419</v>
       </c>
       <c r="O11" t="n">
-        <v>1867721.957402</v>
+        <v>1875378.99781</v>
       </c>
       <c r="P11" t="n">
-        <v>2090765.320981</v>
+        <v>2100400.951015</v>
       </c>
       <c r="Q11" t="n">
-        <v>2302452.272731</v>
+        <v>2314379.737824</v>
       </c>
       <c r="R11" t="n">
-        <v>2484642.779678</v>
+        <v>2499181.348041</v>
       </c>
       <c r="S11" t="n">
-        <v>2633602.912685</v>
+        <v>2651214.946471</v>
       </c>
       <c r="T11" t="n">
-        <v>2723249.915523</v>
+        <v>2744454.621299</v>
       </c>
       <c r="U11" t="n">
-        <v>2779741.681168</v>
+        <v>2805642.545554</v>
       </c>
       <c r="V11" t="n">
-        <v>2800577.817864</v>
+        <v>2832962.290058</v>
       </c>
     </row>
     <row r="12">
@@ -1286,58 +1286,58 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>482590.170506</v>
+        <v>482494.670609</v>
       </c>
       <c r="F12" t="n">
-        <v>495945.697579</v>
+        <v>495756.510713</v>
       </c>
       <c r="G12" t="n">
-        <v>597040.78759</v>
+        <v>596706.598704</v>
       </c>
       <c r="H12" t="n">
-        <v>746676.252053</v>
+        <v>746126.831842</v>
       </c>
       <c r="I12" t="n">
-        <v>930802.6410769999</v>
+        <v>929954.3600850001</v>
       </c>
       <c r="J12" t="n">
-        <v>1209249.942149</v>
+        <v>1207933.830056</v>
       </c>
       <c r="K12" t="n">
-        <v>1572420.96973</v>
+        <v>1570425.777529</v>
       </c>
       <c r="L12" t="n">
-        <v>1942162.303407</v>
+        <v>1939339.098485</v>
       </c>
       <c r="M12" t="n">
-        <v>2363993.003151</v>
+        <v>2360104.763021</v>
       </c>
       <c r="N12" t="n">
-        <v>2834670.718928</v>
+        <v>2829437.775263</v>
       </c>
       <c r="O12" t="n">
-        <v>3345155.344273</v>
+        <v>3338254.550929</v>
       </c>
       <c r="P12" t="n">
-        <v>3847566.112702</v>
+        <v>3838702.792494</v>
       </c>
       <c r="Q12" t="n">
-        <v>4351611.290052</v>
+        <v>4340384.453053</v>
       </c>
       <c r="R12" t="n">
-        <v>4835242.189618</v>
+        <v>4821178.366438</v>
       </c>
       <c r="S12" t="n">
-        <v>5309653.552552</v>
+        <v>5292059.141343</v>
       </c>
       <c r="T12" t="n">
-        <v>5722971.778262</v>
+        <v>5701023.542032</v>
       </c>
       <c r="U12" t="n">
-        <v>6201090.228098</v>
+        <v>6172948.358208</v>
       </c>
       <c r="V12" t="n">
-        <v>6701352.272647</v>
+        <v>6664170.904924</v>
       </c>
     </row>
     <row r="13">
@@ -1362,58 +1362,58 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>512779.264121</v>
+        <v>512791.902851</v>
       </c>
       <c r="F13" t="n">
-        <v>510022.601288</v>
+        <v>510055.588325</v>
       </c>
       <c r="G13" t="n">
-        <v>568102.882619</v>
+        <v>568172.563649</v>
       </c>
       <c r="H13" t="n">
-        <v>673699.464681</v>
+        <v>673827.20864</v>
       </c>
       <c r="I13" t="n">
-        <v>826376.4534070001</v>
+        <v>826590.311064</v>
       </c>
       <c r="J13" t="n">
-        <v>1075126.619492</v>
+        <v>1075478.485959</v>
       </c>
       <c r="K13" t="n">
-        <v>1425445.968955</v>
+        <v>1426004.187103</v>
       </c>
       <c r="L13" t="n">
-        <v>1805348.642422</v>
+        <v>1806166.837669</v>
       </c>
       <c r="M13" t="n">
-        <v>2259405.045495</v>
+        <v>2260565.84724</v>
       </c>
       <c r="N13" t="n">
-        <v>2785647.031348</v>
+        <v>2787258.198074</v>
       </c>
       <c r="O13" t="n">
-        <v>3373590.322292</v>
+        <v>3375788.857457</v>
       </c>
       <c r="P13" t="n">
-        <v>3959129.658422</v>
+        <v>3962048.587469</v>
       </c>
       <c r="Q13" t="n">
-        <v>4538169.678209</v>
+        <v>4541983.630761</v>
       </c>
       <c r="R13" t="n">
-        <v>5080339.096286</v>
+        <v>5085251.890256</v>
       </c>
       <c r="S13" t="n">
-        <v>5589350.374499</v>
+        <v>5595649.679609</v>
       </c>
       <c r="T13" t="n">
-        <v>6012803.411645</v>
+        <v>6020849.570487</v>
       </c>
       <c r="U13" t="n">
-        <v>6395683.30372</v>
+        <v>6406189.010204</v>
       </c>
       <c r="V13" t="n">
-        <v>6712773.234262</v>
+        <v>6726976.829815</v>
       </c>
     </row>
     <row r="14">
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1098.939824</v>
+        <v>1098.725548</v>
       </c>
       <c r="F14" t="n">
-        <v>1143.687715</v>
+        <v>1143.117075</v>
       </c>
       <c r="G14" t="n">
-        <v>1986.501747</v>
+        <v>1984.441844</v>
       </c>
       <c r="H14" t="n">
-        <v>3133.523351</v>
+        <v>3126.713582</v>
       </c>
       <c r="I14" t="n">
-        <v>4568.391935</v>
+        <v>4542.944411</v>
       </c>
       <c r="J14" t="n">
         <v>457724.924408</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>203617.054828</v>
+        <v>203617.198477</v>
       </c>
       <c r="F15" t="n">
-        <v>230833.367652</v>
+        <v>230833.699361</v>
       </c>
       <c r="G15" t="n">
-        <v>413210.430247</v>
+        <v>413211.491564</v>
       </c>
       <c r="H15" t="n">
-        <v>651319.35357</v>
+        <v>651322.66611</v>
       </c>
       <c r="I15" t="n">
-        <v>911869.170092</v>
+        <v>911881.364983</v>
       </c>
       <c r="J15" t="n">
         <v>1089312.120846</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25203.288425</v>
+        <v>25203.168298</v>
       </c>
       <c r="F16" t="n">
-        <v>22645.00007</v>
+        <v>22644.751275</v>
       </c>
       <c r="G16" t="n">
-        <v>32740.251271</v>
+        <v>32739.595464</v>
       </c>
       <c r="H16" t="n">
-        <v>44362.614715</v>
+        <v>44360.93447</v>
       </c>
       <c r="I16" t="n">
-        <v>56432.915914</v>
+        <v>56427.675326</v>
       </c>
       <c r="J16" t="n">
         <v>159157.730247</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73241.152059</v>
+        <v>73241.27523</v>
       </c>
       <c r="F17" t="n">
-        <v>76616.087539</v>
+        <v>76616.402313</v>
       </c>
       <c r="G17" t="n">
-        <v>128898.212414</v>
+        <v>128899.283983</v>
       </c>
       <c r="H17" t="n">
-        <v>192735.728052</v>
+        <v>192739.084162</v>
       </c>
       <c r="I17" t="n">
-        <v>257863.412102</v>
+        <v>257875.373556</v>
       </c>
       <c r="J17" t="n">
         <v>150842.533007</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>51163.806264</v>
+        <v>51163.873847</v>
       </c>
       <c r="F18" t="n">
-        <v>55974.760083</v>
+        <v>55974.933035</v>
       </c>
       <c r="G18" t="n">
-        <v>93243.21161300001</v>
+        <v>93243.794436</v>
       </c>
       <c r="H18" t="n">
-        <v>137835.282607</v>
+        <v>137837.10397</v>
       </c>
       <c r="I18" t="n">
-        <v>185155.481424</v>
+        <v>185162.013191</v>
       </c>
       <c r="J18" t="n">
         <v>149544.177519</v>
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223732.228752</v>
+        <v>223837.430516</v>
       </c>
       <c r="F19" t="n">
-        <v>233669.368743</v>
+        <v>233886.268098</v>
       </c>
       <c r="G19" t="n">
-        <v>244528.131508</v>
+        <v>244871.477598</v>
       </c>
       <c r="H19" t="n">
-        <v>258750.119597</v>
+        <v>259242.386563</v>
       </c>
       <c r="I19" t="n">
-        <v>274916.626861</v>
+        <v>275582.214887</v>
       </c>
       <c r="J19" t="n">
-        <v>316031.977562</v>
+        <v>316966.210192</v>
       </c>
       <c r="K19" t="n">
-        <v>385048.085754</v>
+        <v>386397.70056</v>
       </c>
       <c r="L19" t="n">
-        <v>455778.825805</v>
+        <v>457635.360953</v>
       </c>
       <c r="M19" t="n">
-        <v>531760.089906</v>
+        <v>534244.046695</v>
       </c>
       <c r="N19" t="n">
-        <v>612185.22411</v>
+        <v>615438.306588</v>
       </c>
       <c r="O19" t="n">
-        <v>693316.57056</v>
+        <v>697493.212531</v>
       </c>
       <c r="P19" t="n">
-        <v>771439.22961</v>
+        <v>776705.8706359999</v>
       </c>
       <c r="Q19" t="n">
-        <v>849866.901653</v>
+        <v>856453.641675</v>
       </c>
       <c r="R19" t="n">
-        <v>927861.07346</v>
+        <v>936059.51306</v>
       </c>
       <c r="S19" t="n">
-        <v>1005617.39253</v>
+        <v>1015827.144832</v>
       </c>
       <c r="T19" t="n">
-        <v>1082875.143504</v>
+        <v>1095674.045761</v>
       </c>
       <c r="U19" t="n">
-        <v>1152027.863374</v>
+        <v>1168212.899764</v>
       </c>
       <c r="V19" t="n">
-        <v>1203472.153115</v>
+        <v>1224224.63652</v>
       </c>
     </row>
     <row r="20">
@@ -1894,58 +1894,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21249.512855</v>
+        <v>21267.002738</v>
       </c>
       <c r="F20" t="n">
-        <v>21258.354459</v>
+        <v>21291.777012</v>
       </c>
       <c r="G20" t="n">
-        <v>22650.230998</v>
+        <v>22700.296572</v>
       </c>
       <c r="H20" t="n">
-        <v>24114.869942</v>
+        <v>24182.856314</v>
       </c>
       <c r="I20" t="n">
-        <v>25313.618353</v>
+        <v>25400.811858</v>
       </c>
       <c r="J20" t="n">
-        <v>28101.710296</v>
+        <v>28217.632098</v>
       </c>
       <c r="K20" t="n">
-        <v>32448.973812</v>
+        <v>32607.56984</v>
       </c>
       <c r="L20" t="n">
-        <v>35875.953847</v>
+        <v>36082.568109</v>
       </c>
       <c r="M20" t="n">
-        <v>38871.144829</v>
+        <v>39133.679823</v>
       </c>
       <c r="N20" t="n">
-        <v>41576.565602</v>
+        <v>41904.484467</v>
       </c>
       <c r="O20" t="n">
-        <v>43866.922181</v>
+        <v>44269.211691</v>
       </c>
       <c r="P20" t="n">
-        <v>45489.475541</v>
+        <v>45973.972428</v>
       </c>
       <c r="Q20" t="n">
-        <v>46614.902083</v>
+        <v>47192.970693</v>
       </c>
       <c r="R20" t="n">
-        <v>47133.368828</v>
+        <v>47818.107704</v>
       </c>
       <c r="S20" t="n">
-        <v>47088.045266</v>
+        <v>47896.75842</v>
       </c>
       <c r="T20" t="n">
-        <v>46653.660947</v>
+        <v>47613.9507</v>
       </c>
       <c r="U20" t="n">
-        <v>45699.948993</v>
+        <v>46848.88002</v>
       </c>
       <c r="V20" t="n">
-        <v>44109.153747</v>
+        <v>45501.306322</v>
       </c>
     </row>
     <row r="21">
@@ -1970,58 +1970,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99841.804989</v>
+        <v>99821.122183</v>
       </c>
       <c r="F21" t="n">
-        <v>84265.408832</v>
+        <v>84232.860982</v>
       </c>
       <c r="G21" t="n">
-        <v>76007.566275</v>
+        <v>75966.156875</v>
       </c>
       <c r="H21" t="n">
-        <v>73832.105285</v>
+        <v>73781.617417</v>
       </c>
       <c r="I21" t="n">
-        <v>74980.269826</v>
+        <v>74919.749775</v>
       </c>
       <c r="J21" t="n">
-        <v>83768.614503</v>
+        <v>83691.596232</v>
       </c>
       <c r="K21" t="n">
-        <v>99556.24015899999</v>
+        <v>99454.22687699999</v>
       </c>
       <c r="L21" t="n">
-        <v>114900.84346</v>
+        <v>114771.524152</v>
       </c>
       <c r="M21" t="n">
-        <v>131209.610592</v>
+        <v>131048.782721</v>
       </c>
       <c r="N21" t="n">
-        <v>148844.80806</v>
+        <v>148646.722668</v>
       </c>
       <c r="O21" t="n">
-        <v>167447.111871</v>
+        <v>167205.08985</v>
       </c>
       <c r="P21" t="n">
-        <v>186134.711446</v>
+        <v>185841.676369</v>
       </c>
       <c r="Q21" t="n">
-        <v>204994.599494</v>
+        <v>204641.245502</v>
       </c>
       <c r="R21" t="n">
-        <v>222445.176644</v>
+        <v>222022.650249</v>
       </c>
       <c r="S21" t="n">
-        <v>241749.848977</v>
+        <v>241236.260531</v>
       </c>
       <c r="T21" t="n">
-        <v>261402.559838</v>
+        <v>260770.568431</v>
       </c>
       <c r="U21" t="n">
-        <v>277336.952705</v>
+        <v>276556.129438</v>
       </c>
       <c r="V21" t="n">
-        <v>284691.059886</v>
+        <v>283725.843813</v>
       </c>
     </row>
     <row r="22">
@@ -2046,58 +2046,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>247284.180516</v>
+        <v>247299.776001</v>
       </c>
       <c r="F22" t="n">
-        <v>260712.581834</v>
+        <v>260742.599593</v>
       </c>
       <c r="G22" t="n">
-        <v>274626.899865</v>
+        <v>274674.294723</v>
       </c>
       <c r="H22" t="n">
-        <v>289895.432449</v>
+        <v>289967.797434</v>
       </c>
       <c r="I22" t="n">
-        <v>306533.453056</v>
+        <v>306639.462386</v>
       </c>
       <c r="J22" t="n">
-        <v>351399.924904</v>
+        <v>351558.79765</v>
       </c>
       <c r="K22" t="n">
-        <v>428359.794335</v>
+        <v>428599.857828</v>
       </c>
       <c r="L22" t="n">
-        <v>507618.353173</v>
+        <v>507959.820718</v>
       </c>
       <c r="M22" t="n">
-        <v>593675.03527</v>
+        <v>594146.08923</v>
       </c>
       <c r="N22" t="n">
-        <v>686937.269177</v>
+        <v>687572.168356</v>
       </c>
       <c r="O22" t="n">
-        <v>785797.930731</v>
+        <v>786635.4407799999</v>
       </c>
       <c r="P22" t="n">
-        <v>885266.458246</v>
+        <v>886348.920072</v>
       </c>
       <c r="Q22" t="n">
-        <v>992342.496481</v>
+        <v>993726.878072</v>
       </c>
       <c r="R22" t="n">
-        <v>1105720.115728</v>
+        <v>1107475.491652</v>
       </c>
       <c r="S22" t="n">
-        <v>1224223.196732</v>
+        <v>1226443.379979</v>
       </c>
       <c r="T22" t="n">
-        <v>1345341.442645</v>
+        <v>1348167.755403</v>
       </c>
       <c r="U22" t="n">
-        <v>1455978.490594</v>
+        <v>1459609.403667</v>
       </c>
       <c r="V22" t="n">
-        <v>1539710.099061</v>
+        <v>1544449.274835</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760184.593945</v>
+        <v>760009.809234</v>
       </c>
       <c r="F23" t="n">
-        <v>843057.762809</v>
+        <v>842682.708051</v>
       </c>
       <c r="G23" t="n">
-        <v>957184.797528</v>
+        <v>956565.581969</v>
       </c>
       <c r="H23" t="n">
-        <v>1112000.476816</v>
+        <v>1111078.797624</v>
       </c>
       <c r="I23" t="n">
-        <v>1297344.564938</v>
+        <v>1296059.578978</v>
       </c>
       <c r="J23" t="n">
-        <v>1623203.052707</v>
+        <v>1621357.311401</v>
       </c>
       <c r="K23" t="n">
-        <v>2127418.009904</v>
+        <v>2124705.218646</v>
       </c>
       <c r="L23" t="n">
-        <v>2686968.973845</v>
+        <v>2683182.699543</v>
       </c>
       <c r="M23" t="n">
-        <v>3328473.488621</v>
+        <v>3323337.656957</v>
       </c>
       <c r="N23" t="n">
-        <v>4052026.417243</v>
+        <v>4045212.419556</v>
       </c>
       <c r="O23" t="n">
-        <v>4844381.154321</v>
+        <v>4835515.242407</v>
       </c>
       <c r="P23" t="n">
-        <v>5677098.807914</v>
+        <v>5665769.302509</v>
       </c>
       <c r="Q23" t="n">
-        <v>6563460.464196</v>
+        <v>6549108.420289</v>
       </c>
       <c r="R23" t="n">
-        <v>7487287.246398</v>
+        <v>7469203.249514</v>
       </c>
       <c r="S23" t="n">
-        <v>8444463.405165</v>
+        <v>8421674.018058</v>
       </c>
       <c r="T23" t="n">
-        <v>9432353.935206</v>
+        <v>9403428.097192001</v>
       </c>
       <c r="U23" t="n">
-        <v>10368191.823609</v>
+        <v>10331139.482477</v>
       </c>
       <c r="V23" t="n">
-        <v>11128231.46544</v>
+        <v>11080080.564175</v>
       </c>
     </row>
     <row r="24">
@@ -2198,58 +2198,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11402.946623</v>
+        <v>11419.53756</v>
       </c>
       <c r="F24" t="n">
-        <v>11260.630078</v>
+        <v>11292.456401</v>
       </c>
       <c r="G24" t="n">
-        <v>11610.683416</v>
+        <v>11658.308299</v>
       </c>
       <c r="H24" t="n">
-        <v>12090.592199</v>
+        <v>12155.147545</v>
       </c>
       <c r="I24" t="n">
-        <v>12552.827256</v>
+        <v>12635.366669</v>
       </c>
       <c r="J24" t="n">
-        <v>14014.543761</v>
+        <v>14124.116506</v>
       </c>
       <c r="K24" t="n">
-        <v>16464.941717</v>
+        <v>16614.743874</v>
       </c>
       <c r="L24" t="n">
-        <v>18634.535562</v>
+        <v>18829.549047</v>
       </c>
       <c r="M24" t="n">
-        <v>20659.94234</v>
+        <v>20907.134607</v>
       </c>
       <c r="N24" t="n">
-        <v>22507.683261</v>
+        <v>22814.804886</v>
       </c>
       <c r="O24" t="n">
-        <v>24076.881002</v>
+        <v>24451.399636</v>
       </c>
       <c r="P24" t="n">
-        <v>25249.185352</v>
+        <v>25697.920565</v>
       </c>
       <c r="Q24" t="n">
-        <v>26159.121658</v>
+        <v>26692.784087</v>
       </c>
       <c r="R24" t="n">
-        <v>26735.77966</v>
+        <v>27366.3726</v>
       </c>
       <c r="S24" t="n">
-        <v>27009.876107</v>
+        <v>27753.797166</v>
       </c>
       <c r="T24" t="n">
-        <v>27084.020642</v>
+        <v>27967.223843</v>
       </c>
       <c r="U24" t="n">
-        <v>26928.401314</v>
+        <v>27986.670734</v>
       </c>
       <c r="V24" t="n">
-        <v>26617.762707</v>
+        <v>27908.625904</v>
       </c>
     </row>
     <row r="25">
@@ -2274,58 +2274,58 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>23640.440431</v>
+        <v>23641.830049</v>
       </c>
       <c r="F25" t="n">
-        <v>21462.151333</v>
+        <v>21465.190448</v>
       </c>
       <c r="G25" t="n">
-        <v>20805.659595</v>
+        <v>20810.441774</v>
       </c>
       <c r="H25" t="n">
-        <v>21332.031621</v>
+        <v>21338.726259</v>
       </c>
       <c r="I25" t="n">
-        <v>22357.526977</v>
+        <v>22366.390259</v>
       </c>
       <c r="J25" t="n">
-        <v>25281.530751</v>
+        <v>25293.855642</v>
       </c>
       <c r="K25" t="n">
-        <v>30071.611397</v>
+        <v>30089.40386</v>
       </c>
       <c r="L25" t="n">
-        <v>34480.966128</v>
+        <v>34505.568671</v>
       </c>
       <c r="M25" t="n">
-        <v>38804.035587</v>
+        <v>38837.322013</v>
       </c>
       <c r="N25" t="n">
-        <v>42904.646426</v>
+        <v>42948.804909</v>
       </c>
       <c r="O25" t="n">
-        <v>46512.356768</v>
+        <v>46569.873003</v>
       </c>
       <c r="P25" t="n">
-        <v>49343.294841</v>
+        <v>49416.913843</v>
       </c>
       <c r="Q25" t="n">
-        <v>51560.371839</v>
+        <v>51653.672441</v>
       </c>
       <c r="R25" t="n">
-        <v>52970.601361</v>
+        <v>53087.891872</v>
       </c>
       <c r="S25" t="n">
-        <v>53619.365331</v>
+        <v>53766.47564</v>
       </c>
       <c r="T25" t="n">
-        <v>53656.751394</v>
+        <v>53841.963415</v>
       </c>
       <c r="U25" t="n">
-        <v>52884.076921</v>
+        <v>53118.495672</v>
       </c>
       <c r="V25" t="n">
-        <v>51096.812475</v>
+        <v>51396.7401</v>
       </c>
     </row>
     <row r="26">
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>528107.4758669999</v>
+        <v>528164.007718</v>
       </c>
       <c r="F26" t="n">
-        <v>527913.230612</v>
+        <v>528035.65253</v>
       </c>
       <c r="G26" t="n">
-        <v>519002.648922</v>
+        <v>519210.826646</v>
       </c>
       <c r="H26" t="n">
-        <v>518708.311584</v>
+        <v>519028.354629</v>
       </c>
       <c r="I26" t="n">
-        <v>524815.519721</v>
+        <v>525274.722094</v>
       </c>
       <c r="J26" t="n">
-        <v>579020.611471</v>
+        <v>579694.942926</v>
       </c>
       <c r="K26" t="n">
-        <v>683260.999816</v>
+        <v>684267.107399</v>
       </c>
       <c r="L26" t="n">
-        <v>790577.515299</v>
+        <v>791995.451893</v>
       </c>
       <c r="M26" t="n">
-        <v>908048.091886</v>
+        <v>909983.249399</v>
       </c>
       <c r="N26" t="n">
-        <v>1033476.840836</v>
+        <v>1036053.741249</v>
       </c>
       <c r="O26" t="n">
-        <v>1163303.477545</v>
+        <v>1166669.817858</v>
       </c>
       <c r="P26" t="n">
-        <v>1293059.095388</v>
+        <v>1297380.71235</v>
       </c>
       <c r="Q26" t="n">
-        <v>1429035.643531</v>
+        <v>1434539.664283</v>
       </c>
       <c r="R26" t="n">
-        <v>1570556.210127</v>
+        <v>1577530.777621</v>
       </c>
       <c r="S26" t="n">
-        <v>1719767.142666</v>
+        <v>1728614.502525</v>
       </c>
       <c r="T26" t="n">
-        <v>1879007.596946</v>
+        <v>1890318.671329</v>
       </c>
       <c r="U26" t="n">
-        <v>2033748.65885</v>
+        <v>2048342.239481</v>
       </c>
       <c r="V26" t="n">
-        <v>2164098.351924</v>
+        <v>2183195.084126</v>
       </c>
     </row>
     <row r="27">
@@ -2426,58 +2426,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>287276.518162</v>
+        <v>287271.721589</v>
       </c>
       <c r="F27" t="n">
-        <v>298140.782413</v>
+        <v>298133.239462</v>
       </c>
       <c r="G27" t="n">
-        <v>303292.004077</v>
+        <v>303290.276934</v>
       </c>
       <c r="H27" t="n">
-        <v>316236.051205</v>
+        <v>316248.993363</v>
       </c>
       <c r="I27" t="n">
-        <v>337213.633102</v>
+        <v>337249.102087</v>
       </c>
       <c r="J27" t="n">
-        <v>393398.433856</v>
+        <v>393468.224219</v>
       </c>
       <c r="K27" t="n">
-        <v>488071.254514</v>
+        <v>488195.20457</v>
       </c>
       <c r="L27" t="n">
-        <v>588271.81064</v>
+        <v>588469.81684</v>
       </c>
       <c r="M27" t="n">
-        <v>698302.332534</v>
+        <v>698602.04056</v>
       </c>
       <c r="N27" t="n">
-        <v>815126.842034</v>
+        <v>815563.96566</v>
       </c>
       <c r="O27" t="n">
-        <v>932137.638194</v>
+        <v>932757.655666</v>
       </c>
       <c r="P27" t="n">
-        <v>1042470.811769</v>
+        <v>1043329.690462</v>
       </c>
       <c r="Q27" t="n">
-        <v>1152014.623144</v>
+        <v>1153183.204875</v>
       </c>
       <c r="R27" t="n">
-        <v>1258241.558975</v>
+        <v>1259808.588676</v>
       </c>
       <c r="S27" t="n">
-        <v>1360505.650603</v>
+        <v>1362593.536075</v>
       </c>
       <c r="T27" t="n">
-        <v>1456386.797683</v>
+        <v>1459171.445595</v>
       </c>
       <c r="U27" t="n">
-        <v>1533006.613307</v>
+        <v>1536737.002369</v>
       </c>
       <c r="V27" t="n">
-        <v>1575248.126619</v>
+        <v>1580291.881505</v>
       </c>
     </row>
     <row r="28">
@@ -2502,58 +2502,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>95741.97606099999</v>
+        <v>95729.44061400001</v>
       </c>
       <c r="F28" t="n">
-        <v>90189.524886</v>
+        <v>90167.043423</v>
       </c>
       <c r="G28" t="n">
-        <v>100458.855846</v>
+        <v>100419.81664</v>
       </c>
       <c r="H28" t="n">
-        <v>119960.366213</v>
+        <v>119895.679764</v>
       </c>
       <c r="I28" t="n">
-        <v>144463.437536</v>
+        <v>144364.078634</v>
       </c>
       <c r="J28" t="n">
-        <v>183846.714029</v>
+        <v>183694.426974</v>
       </c>
       <c r="K28" t="n">
-        <v>240528.637474</v>
+        <v>240297.515427</v>
       </c>
       <c r="L28" t="n">
-        <v>298403.879159</v>
+        <v>298079.296992</v>
       </c>
       <c r="M28" t="n">
-        <v>359743.316912</v>
+        <v>359307.086471</v>
       </c>
       <c r="N28" t="n">
-        <v>424538.743886</v>
+        <v>423969.622297</v>
       </c>
       <c r="O28" t="n">
-        <v>492477.907677</v>
+        <v>491751.007428</v>
       </c>
       <c r="P28" t="n">
-        <v>562079.637069</v>
+        <v>561165.727942</v>
       </c>
       <c r="Q28" t="n">
-        <v>635568.661026</v>
+        <v>634425.303187</v>
       </c>
       <c r="R28" t="n">
-        <v>709556.0054800001</v>
+        <v>708134.493711</v>
       </c>
       <c r="S28" t="n">
-        <v>782380.334383</v>
+        <v>780618.3845329999</v>
       </c>
       <c r="T28" t="n">
-        <v>853308.057975</v>
+        <v>851116.245111</v>
       </c>
       <c r="U28" t="n">
-        <v>916238.499034</v>
+        <v>913490.125078</v>
       </c>
       <c r="V28" t="n">
-        <v>962515.641224</v>
+        <v>959016.668899</v>
       </c>
     </row>
     <row r="29">
@@ -2578,58 +2578,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>142037.559035</v>
+        <v>142045.561755</v>
       </c>
       <c r="F29" t="n">
-        <v>122054.628799</v>
+        <v>122081.034147</v>
       </c>
       <c r="G29" t="n">
-        <v>113120.000469</v>
+        <v>113173.622497</v>
       </c>
       <c r="H29" t="n">
-        <v>110397.864565</v>
+        <v>110482.138312</v>
       </c>
       <c r="I29" t="n">
-        <v>116060.350263</v>
+        <v>116180.17656</v>
       </c>
       <c r="J29" t="n">
-        <v>132744.403527</v>
+        <v>132911.564907</v>
       </c>
       <c r="K29" t="n">
-        <v>155641.686877</v>
+        <v>155865.284595</v>
       </c>
       <c r="L29" t="n">
-        <v>177595.139746</v>
+        <v>177873.268987</v>
       </c>
       <c r="M29" t="n">
-        <v>203571.218246</v>
+        <v>203909.422312</v>
       </c>
       <c r="N29" t="n">
-        <v>234305.50288</v>
+        <v>234712.230808</v>
       </c>
       <c r="O29" t="n">
-        <v>267961.814693</v>
+        <v>268443.157951</v>
       </c>
       <c r="P29" t="n">
-        <v>303263.855441</v>
+        <v>303823.668744</v>
       </c>
       <c r="Q29" t="n">
-        <v>341618.657403</v>
+        <v>342263.633051</v>
       </c>
       <c r="R29" t="n">
-        <v>380906.34187</v>
+        <v>381637.050168</v>
       </c>
       <c r="S29" t="n">
-        <v>422357.267147</v>
+        <v>423175.376814</v>
       </c>
       <c r="T29" t="n">
-        <v>465219.225138</v>
+        <v>466125.040332</v>
       </c>
       <c r="U29" t="n">
-        <v>509018.950198</v>
+        <v>510011.424484</v>
       </c>
       <c r="V29" t="n">
-        <v>555103.269946</v>
+        <v>556185.005256</v>
       </c>
     </row>
     <row r="30">
@@ -2654,58 +2654,58 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>236673.178424</v>
+        <v>236686.158656</v>
       </c>
       <c r="F30" t="n">
-        <v>189930.832614</v>
+        <v>189979.618381</v>
       </c>
       <c r="G30" t="n">
-        <v>165655.829734</v>
+        <v>165754.475867</v>
       </c>
       <c r="H30" t="n">
-        <v>158071.441798</v>
+        <v>158223.345769</v>
       </c>
       <c r="I30" t="n">
-        <v>162823.512823</v>
+        <v>163038.135755</v>
       </c>
       <c r="J30" t="n">
-        <v>184585.571244</v>
+        <v>184885.134294</v>
       </c>
       <c r="K30" t="n">
-        <v>215450.411187</v>
+        <v>215853.077017</v>
       </c>
       <c r="L30" t="n">
-        <v>247111.914896</v>
+        <v>247617.600046</v>
       </c>
       <c r="M30" t="n">
-        <v>288884.062301</v>
+        <v>289506.656363</v>
       </c>
       <c r="N30" t="n">
-        <v>343564.333289</v>
+        <v>344321.76283</v>
       </c>
       <c r="O30" t="n">
-        <v>409231.309987</v>
+        <v>410136.531952</v>
       </c>
       <c r="P30" t="n">
-        <v>484294.987125</v>
+        <v>485358.013727</v>
       </c>
       <c r="Q30" t="n">
-        <v>570796.3905569999</v>
+        <v>572030.910785</v>
       </c>
       <c r="R30" t="n">
-        <v>664803.997132</v>
+        <v>666215.347223</v>
       </c>
       <c r="S30" t="n">
-        <v>768248.213772</v>
+        <v>769844.596262</v>
       </c>
       <c r="T30" t="n">
-        <v>879062.194575</v>
+        <v>880848.52441</v>
       </c>
       <c r="U30" t="n">
-        <v>1001347.700303</v>
+        <v>1003324.28955</v>
       </c>
       <c r="V30" t="n">
-        <v>1139854.333589</v>
+        <v>1142023.568279</v>
       </c>
     </row>
     <row r="31">
@@ -2730,58 +2730,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>407569.675223</v>
+        <v>407419.027555</v>
       </c>
       <c r="F31" t="n">
-        <v>357920.700515</v>
+        <v>357695.598693</v>
       </c>
       <c r="G31" t="n">
-        <v>323216.310723</v>
+        <v>322973.894068</v>
       </c>
       <c r="H31" t="n">
-        <v>309302.141777</v>
+        <v>309054.036934</v>
       </c>
       <c r="I31" t="n">
-        <v>319871.549612</v>
+        <v>319603.09498</v>
       </c>
       <c r="J31" t="n">
-        <v>361383.35602</v>
+        <v>361062.708946</v>
       </c>
       <c r="K31" t="n">
-        <v>418227.514669</v>
+        <v>417830.208653</v>
       </c>
       <c r="L31" t="n">
-        <v>470246.904957</v>
+        <v>469765.323074</v>
       </c>
       <c r="M31" t="n">
-        <v>533288.6297</v>
+        <v>532699.909382</v>
       </c>
       <c r="N31" t="n">
-        <v>611313.288736</v>
+        <v>610588.967126</v>
       </c>
       <c r="O31" t="n">
-        <v>699927.940756</v>
+        <v>699043.2397790001</v>
       </c>
       <c r="P31" t="n">
-        <v>795910.306826</v>
+        <v>794844.5132470001</v>
       </c>
       <c r="Q31" t="n">
-        <v>902900.2865019999</v>
+        <v>901626.4074509999</v>
       </c>
       <c r="R31" t="n">
-        <v>1014468.557894</v>
+        <v>1012966.57036</v>
       </c>
       <c r="S31" t="n">
-        <v>1133136.766291</v>
+        <v>1131380.046814</v>
       </c>
       <c r="T31" t="n">
-        <v>1255693.719448</v>
+        <v>1253658.246699</v>
       </c>
       <c r="U31" t="n">
-        <v>1380638.713225</v>
+        <v>1378297.99268</v>
       </c>
       <c r="V31" t="n">
-        <v>1511161.49309</v>
+        <v>1508477.130836</v>
       </c>
     </row>
     <row r="32">
@@ -2806,58 +2806,58 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>364936.140578</v>
+        <v>364933.944579</v>
       </c>
       <c r="F32" t="n">
-        <v>287353.651872</v>
+        <v>287385.952323</v>
       </c>
       <c r="G32" t="n">
-        <v>244685.463507</v>
+        <v>244771.488886</v>
       </c>
       <c r="H32" t="n">
-        <v>228295.636274</v>
+        <v>228434.877551</v>
       </c>
       <c r="I32" t="n">
-        <v>237675.28997</v>
+        <v>237869.403486</v>
       </c>
       <c r="J32" t="n">
-        <v>275457.319962</v>
+        <v>275718.299687</v>
       </c>
       <c r="K32" t="n">
-        <v>330550.748819</v>
+        <v>330883.721898</v>
       </c>
       <c r="L32" t="n">
-        <v>385772.956315</v>
+        <v>386165.825412</v>
       </c>
       <c r="M32" t="n">
-        <v>450556.714583</v>
+        <v>451008.329331</v>
       </c>
       <c r="N32" t="n">
-        <v>524174.569061</v>
+        <v>524688.338357</v>
       </c>
       <c r="O32" t="n">
-        <v>601472.711811</v>
+        <v>602051.06251</v>
       </c>
       <c r="P32" t="n">
-        <v>678400.94542</v>
+        <v>679044.991831</v>
       </c>
       <c r="Q32" t="n">
-        <v>757789.343806</v>
+        <v>758504.124678</v>
       </c>
       <c r="R32" t="n">
-        <v>833261.127415</v>
+        <v>834047.295242</v>
       </c>
       <c r="S32" t="n">
-        <v>918579.050865</v>
+        <v>919429.735431</v>
       </c>
       <c r="T32" t="n">
-        <v>1008445.192435</v>
+        <v>1009356.118378</v>
       </c>
       <c r="U32" t="n">
-        <v>1094596.256703</v>
+        <v>1095566.532097</v>
       </c>
       <c r="V32" t="n">
-        <v>1171822.538636</v>
+        <v>1172864.130435</v>
       </c>
     </row>
     <row r="33">
@@ -2882,58 +2882,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>379286.243618</v>
+        <v>379304.13765</v>
       </c>
       <c r="F33" t="n">
-        <v>324985.162044</v>
+        <v>325042.986639</v>
       </c>
       <c r="G33" t="n">
-        <v>299262.509637</v>
+        <v>299380.122946</v>
       </c>
       <c r="H33" t="n">
-        <v>291781.929906</v>
+        <v>291965.393019</v>
       </c>
       <c r="I33" t="n">
-        <v>306866.454717</v>
+        <v>307123.877507</v>
       </c>
       <c r="J33" t="n">
-        <v>349804.6674</v>
+        <v>350157.065778</v>
       </c>
       <c r="K33" t="n">
-        <v>405642.706174</v>
+        <v>406102.606972</v>
       </c>
       <c r="L33" t="n">
-        <v>454709.180255</v>
+        <v>455266.873199</v>
       </c>
       <c r="M33" t="n">
-        <v>511141.765741</v>
+        <v>511803.991785</v>
       </c>
       <c r="N33" t="n">
-        <v>576172.877998</v>
+        <v>576950.673298</v>
       </c>
       <c r="O33" t="n">
-        <v>644761.923604</v>
+        <v>645661.840131</v>
       </c>
       <c r="P33" t="n">
-        <v>712446.191978</v>
+        <v>713472.754453</v>
       </c>
       <c r="Q33" t="n">
-        <v>780987.830172</v>
+        <v>782151.87417</v>
       </c>
       <c r="R33" t="n">
-        <v>844189.901981</v>
+        <v>845492.532869</v>
       </c>
       <c r="S33" t="n">
-        <v>921578.912352</v>
+        <v>923014.633619</v>
       </c>
       <c r="T33" t="n">
-        <v>1006788.100909</v>
+        <v>1008349.705827</v>
       </c>
       <c r="U33" t="n">
-        <v>1089751.832057</v>
+        <v>1091438.333078</v>
       </c>
       <c r="V33" t="n">
-        <v>1162038.112857</v>
+        <v>1163859.43906</v>
       </c>
     </row>
     <row r="34">
@@ -2958,58 +2958,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1604030.407835</v>
+        <v>1603680.393784</v>
       </c>
       <c r="F34" t="n">
-        <v>2408421.833962</v>
+        <v>2407340.863901</v>
       </c>
       <c r="G34" t="n">
-        <v>3751707.834344</v>
+        <v>3749427.143604</v>
       </c>
       <c r="H34" t="n">
-        <v>5278611.839244</v>
+        <v>5274910.626951</v>
       </c>
       <c r="I34" t="n">
-        <v>7008831.401963</v>
+        <v>7003440.87312</v>
       </c>
       <c r="J34" t="n">
-        <v>9170718.758266</v>
+        <v>9163055.637495</v>
       </c>
       <c r="K34" t="n">
-        <v>11494151.176355</v>
+        <v>11483736.812997</v>
       </c>
       <c r="L34" t="n">
-        <v>13440068.425835</v>
+        <v>13426897.483788</v>
       </c>
       <c r="M34" t="n">
-        <v>15411538.583933</v>
+        <v>15395300.649972</v>
       </c>
       <c r="N34" t="n">
-        <v>17565073.740744</v>
+        <v>17545321.904746</v>
       </c>
       <c r="O34" t="n">
-        <v>19837229.402175</v>
+        <v>19813601.021951</v>
       </c>
       <c r="P34" t="n">
-        <v>22169404.758488</v>
+        <v>22141634.933474</v>
       </c>
       <c r="Q34" t="n">
-        <v>24639220.405918</v>
+        <v>24606952.506292</v>
       </c>
       <c r="R34" t="n">
-        <v>27029227.959131</v>
+        <v>26992378.403017</v>
       </c>
       <c r="S34" t="n">
-        <v>29346731.808941</v>
+        <v>29305185.960683</v>
       </c>
       <c r="T34" t="n">
-        <v>31477529.38159</v>
+        <v>31431355.235479</v>
       </c>
       <c r="U34" t="n">
-        <v>33361808.009504</v>
+        <v>33311104.29792</v>
       </c>
       <c r="V34" t="n">
-        <v>35082341.985696</v>
+        <v>35027003.20696</v>
       </c>
     </row>
     <row r="35">
@@ -3034,58 +3034,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>92183.47710400001</v>
+        <v>92187.25750199999</v>
       </c>
       <c r="F35" t="n">
-        <v>97492.158432</v>
+        <v>97498.509189</v>
       </c>
       <c r="G35" t="n">
-        <v>108025.111687</v>
+        <v>108038.206152</v>
       </c>
       <c r="H35" t="n">
-        <v>116647.11421</v>
+        <v>116673.018792</v>
       </c>
       <c r="I35" t="n">
-        <v>126898.752318</v>
+        <v>126942.642932</v>
       </c>
       <c r="J35" t="n">
-        <v>143505.214625</v>
+        <v>143573.148783</v>
       </c>
       <c r="K35" t="n">
-        <v>162284.11571</v>
+        <v>162379.898185</v>
       </c>
       <c r="L35" t="n">
-        <v>176774.156057</v>
+        <v>176896.500749</v>
       </c>
       <c r="M35" t="n">
-        <v>193303.348746</v>
+        <v>193454.285356</v>
       </c>
       <c r="N35" t="n">
-        <v>212412.681875</v>
+        <v>212595.816724</v>
       </c>
       <c r="O35" t="n">
-        <v>231707.502279</v>
+        <v>231925.85976</v>
       </c>
       <c r="P35" t="n">
-        <v>249624.602586</v>
+        <v>249881.087315</v>
       </c>
       <c r="Q35" t="n">
-        <v>266884.737824</v>
+        <v>267183.691146</v>
       </c>
       <c r="R35" t="n">
-        <v>281601.83937</v>
+        <v>281944.682412</v>
       </c>
       <c r="S35" t="n">
-        <v>299679.182317</v>
+        <v>300064.49988</v>
       </c>
       <c r="T35" t="n">
-        <v>319032.524649</v>
+        <v>319458.849608</v>
       </c>
       <c r="U35" t="n">
-        <v>336733.372419</v>
+        <v>337200.91724</v>
       </c>
       <c r="V35" t="n">
-        <v>350717.933065</v>
+        <v>351230.188988</v>
       </c>
     </row>
     <row r="36">
@@ -3110,58 +3110,58 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>43643.666429</v>
+        <v>43630.86472</v>
       </c>
       <c r="F36" t="n">
-        <v>37102.366548</v>
+        <v>37084.284517</v>
       </c>
       <c r="G36" t="n">
-        <v>30108.518295</v>
+        <v>30092.471642</v>
       </c>
       <c r="H36" t="n">
-        <v>25156.895029</v>
+        <v>25144.345867</v>
       </c>
       <c r="I36" t="n">
-        <v>22858.70515</v>
+        <v>22848.504094</v>
       </c>
       <c r="J36" t="n">
-        <v>23112.210033</v>
+        <v>23102.757952</v>
       </c>
       <c r="K36" t="n">
-        <v>24278.578912</v>
+        <v>24269.054008</v>
       </c>
       <c r="L36" t="n">
-        <v>24992.233685</v>
+        <v>24982.416046</v>
       </c>
       <c r="M36" t="n">
-        <v>25951.203305</v>
+        <v>25940.777744</v>
       </c>
       <c r="N36" t="n">
-        <v>27122.017705</v>
+        <v>27110.843139</v>
       </c>
       <c r="O36" t="n">
-        <v>28369.109252</v>
+        <v>28357.159902</v>
       </c>
       <c r="P36" t="n">
-        <v>29656.515607</v>
+        <v>29643.778909</v>
       </c>
       <c r="Q36" t="n">
-        <v>31100.979477</v>
+        <v>31087.380007</v>
       </c>
       <c r="R36" t="n">
-        <v>32323.567718</v>
+        <v>32309.305039</v>
       </c>
       <c r="S36" t="n">
-        <v>33363.982611</v>
+        <v>33349.290326</v>
       </c>
       <c r="T36" t="n">
-        <v>34185.286501</v>
+        <v>34170.480522</v>
       </c>
       <c r="U36" t="n">
-        <v>35486.601058</v>
+        <v>35470.957366</v>
       </c>
       <c r="V36" t="n">
-        <v>37159.934583</v>
+        <v>37142.904162</v>
       </c>
     </row>
     <row r="37">
@@ -3186,58 +3186,58 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223742.875945</v>
+        <v>223671.650223</v>
       </c>
       <c r="F37" t="n">
-        <v>170097.610817</v>
+        <v>170010.419407</v>
       </c>
       <c r="G37" t="n">
-        <v>138285.840995</v>
+        <v>138208.06249</v>
       </c>
       <c r="H37" t="n">
-        <v>121556.92494</v>
+        <v>121490.868293</v>
       </c>
       <c r="I37" t="n">
-        <v>117698.338252</v>
+        <v>117637.880231</v>
       </c>
       <c r="J37" t="n">
-        <v>125468.564452</v>
+        <v>125406.00074</v>
       </c>
       <c r="K37" t="n">
-        <v>137230.86961</v>
+        <v>137162.207864</v>
       </c>
       <c r="L37" t="n">
-        <v>145461.734575</v>
+        <v>145387.022999</v>
       </c>
       <c r="M37" t="n">
-        <v>154717.664037</v>
+        <v>154635.516003</v>
       </c>
       <c r="N37" t="n">
-        <v>165200.189737</v>
+        <v>165109.943633</v>
       </c>
       <c r="O37" t="n">
-        <v>175485.844864</v>
+        <v>175387.85721</v>
       </c>
       <c r="P37" t="n">
-        <v>184538.59064</v>
+        <v>184434.352706</v>
       </c>
       <c r="Q37" t="n">
-        <v>196168.417688</v>
+        <v>196054.98018</v>
       </c>
       <c r="R37" t="n">
-        <v>207679.084327</v>
+        <v>207555.777195</v>
       </c>
       <c r="S37" t="n">
-        <v>217896.313142</v>
+        <v>217764.22985</v>
       </c>
       <c r="T37" t="n">
-        <v>225618.478631</v>
+        <v>225480.270851</v>
       </c>
       <c r="U37" t="n">
-        <v>231565.809088</v>
+        <v>231422.603038</v>
       </c>
       <c r="V37" t="n">
-        <v>237266.190413</v>
+        <v>237117.376289</v>
       </c>
     </row>
     <row r="38">
@@ -3262,58 +3262,58 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>236678.043896</v>
+        <v>236780.269946</v>
       </c>
       <c r="F38" t="n">
-        <v>206471.299429</v>
+        <v>206660.248705</v>
       </c>
       <c r="G38" t="n">
-        <v>184663.94682</v>
+        <v>184941.628514</v>
       </c>
       <c r="H38" t="n">
-        <v>176075.946956</v>
+        <v>176443.929244</v>
       </c>
       <c r="I38" t="n">
-        <v>184175.072411</v>
+        <v>184653.599978</v>
       </c>
       <c r="J38" t="n">
-        <v>213092.128844</v>
+        <v>213730.20862</v>
       </c>
       <c r="K38" t="n">
-        <v>254267.426606</v>
+        <v>255102.528519</v>
       </c>
       <c r="L38" t="n">
-        <v>294951.177371</v>
+        <v>295980.779309</v>
       </c>
       <c r="M38" t="n">
-        <v>343328.930637</v>
+        <v>344578.162053</v>
       </c>
       <c r="N38" t="n">
-        <v>400688.936672</v>
+        <v>402192.589311</v>
       </c>
       <c r="O38" t="n">
-        <v>463698.406085</v>
+        <v>465482.340686</v>
       </c>
       <c r="P38" t="n">
-        <v>529312.459163</v>
+        <v>531394.217726</v>
       </c>
       <c r="Q38" t="n">
-        <v>599031.595679</v>
+        <v>601438.621042</v>
       </c>
       <c r="R38" t="n">
-        <v>667035.18929</v>
+        <v>669775.362371</v>
       </c>
       <c r="S38" t="n">
-        <v>733887.932388</v>
+        <v>736977.55884</v>
       </c>
       <c r="T38" t="n">
-        <v>796650.206595</v>
+        <v>800098.440973</v>
       </c>
       <c r="U38" t="n">
-        <v>853740.19647</v>
+        <v>857555.238483</v>
       </c>
       <c r="V38" t="n">
-        <v>907476.002918</v>
+        <v>911682.07109</v>
       </c>
     </row>
     <row r="39">
@@ -3338,58 +3338,58 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>921804.399908</v>
+        <v>921467.848105</v>
       </c>
       <c r="F39" t="n">
-        <v>769460.902773</v>
+        <v>768986.2711510001</v>
       </c>
       <c r="G39" t="n">
-        <v>714631.8889960001</v>
+        <v>714104.984954</v>
       </c>
       <c r="H39" t="n">
-        <v>711878.0123919999</v>
+        <v>711312.895396</v>
       </c>
       <c r="I39" t="n">
-        <v>761599.005461</v>
+        <v>760961.324823</v>
       </c>
       <c r="J39" t="n">
-        <v>881994.355736</v>
+        <v>881207.407371</v>
       </c>
       <c r="K39" t="n">
-        <v>1038828.699205</v>
+        <v>1037829.756616</v>
       </c>
       <c r="L39" t="n">
-        <v>1180917.722215</v>
+        <v>1179687.605784</v>
       </c>
       <c r="M39" t="n">
-        <v>1338375.208104</v>
+        <v>1336868.96198</v>
       </c>
       <c r="N39" t="n">
-        <v>1510042.613093</v>
+        <v>1508221.017261</v>
       </c>
       <c r="O39" t="n">
-        <v>1684743.895253</v>
+        <v>1682585.302839</v>
       </c>
       <c r="P39" t="n">
-        <v>1858798.714567</v>
+        <v>1856290.231748</v>
       </c>
       <c r="Q39" t="n">
-        <v>2046148.333056</v>
+        <v>2043257.45934</v>
       </c>
       <c r="R39" t="n">
-        <v>2235371.663785</v>
+        <v>2232077.454926</v>
       </c>
       <c r="S39" t="n">
-        <v>2435165.775861</v>
+        <v>2431429.051718</v>
       </c>
       <c r="T39" t="n">
-        <v>2661275.373124</v>
+        <v>2657020.904291</v>
       </c>
       <c r="U39" t="n">
-        <v>2909074.165195</v>
+        <v>2904221.253794</v>
       </c>
       <c r="V39" t="n">
-        <v>3177568.051048</v>
+        <v>3172023.854611</v>
       </c>
     </row>
     <row r="40">
@@ -3414,58 +3414,58 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>140808.388584</v>
+        <v>140757.826733</v>
       </c>
       <c r="F40" t="n">
-        <v>121682.667333</v>
+        <v>121608.725181</v>
       </c>
       <c r="G40" t="n">
-        <v>110717.222257</v>
+        <v>110637.383487</v>
       </c>
       <c r="H40" t="n">
-        <v>104879.429223</v>
+        <v>104799.209794</v>
       </c>
       <c r="I40" t="n">
-        <v>108122.277293</v>
+        <v>108036.293778</v>
       </c>
       <c r="J40" t="n">
-        <v>121282.568612</v>
+        <v>121181.119292</v>
       </c>
       <c r="K40" t="n">
-        <v>140185.821462</v>
+        <v>140060.446789</v>
       </c>
       <c r="L40" t="n">
-        <v>158132.248949</v>
+        <v>157979.544855</v>
       </c>
       <c r="M40" t="n">
-        <v>180343.247884</v>
+        <v>180154.870487</v>
       </c>
       <c r="N40" t="n">
-        <v>206924.568346</v>
+        <v>206692.007644</v>
       </c>
       <c r="O40" t="n">
-        <v>235937.763248</v>
+        <v>235654.608434</v>
       </c>
       <c r="P40" t="n">
-        <v>265896.2144</v>
+        <v>265558.297856</v>
       </c>
       <c r="Q40" t="n">
-        <v>299689.010794</v>
+        <v>299287.783754</v>
       </c>
       <c r="R40" t="n">
-        <v>335404.964291</v>
+        <v>334933.404329</v>
       </c>
       <c r="S40" t="n">
-        <v>373516.910237</v>
+        <v>372966.376548</v>
       </c>
       <c r="T40" t="n">
-        <v>412302.50502</v>
+        <v>411666.602165</v>
       </c>
       <c r="U40" t="n">
-        <v>450733.273214</v>
+        <v>450005.987569</v>
       </c>
       <c r="V40" t="n">
-        <v>489445.741311</v>
+        <v>488618.417388</v>
       </c>
     </row>
     <row r="41">
@@ -3490,58 +3490,58 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>165718.666939</v>
+        <v>165662.861509</v>
       </c>
       <c r="F41" t="n">
-        <v>158172.9973</v>
+        <v>158082.306077</v>
       </c>
       <c r="G41" t="n">
-        <v>148554.923334</v>
+        <v>148454.822825</v>
       </c>
       <c r="H41" t="n">
-        <v>143641.114807</v>
+        <v>143539.816769</v>
       </c>
       <c r="I41" t="n">
-        <v>148545.492114</v>
+        <v>148438.2939</v>
       </c>
       <c r="J41" t="n">
-        <v>166759.322174</v>
+        <v>166634.399139</v>
       </c>
       <c r="K41" t="n">
-        <v>190694.243966</v>
+        <v>190543.307467</v>
       </c>
       <c r="L41" t="n">
-        <v>210598.233307</v>
+        <v>210420.233383</v>
       </c>
       <c r="M41" t="n">
-        <v>232798.87676</v>
+        <v>232588.492139</v>
       </c>
       <c r="N41" t="n">
-        <v>257447.130297</v>
+        <v>257199.905132</v>
       </c>
       <c r="O41" t="n">
-        <v>281610.49237</v>
+        <v>281325.870992</v>
       </c>
       <c r="P41" t="n">
-        <v>305010.910668</v>
+        <v>304689.175914</v>
       </c>
       <c r="Q41" t="n">
-        <v>329828.481017</v>
+        <v>329467.226721</v>
       </c>
       <c r="R41" t="n">
-        <v>353754.917757</v>
+        <v>353353.995238</v>
       </c>
       <c r="S41" t="n">
-        <v>377188.434196</v>
+        <v>376746.971418</v>
       </c>
       <c r="T41" t="n">
-        <v>398739.126514</v>
+        <v>398258.287088</v>
       </c>
       <c r="U41" t="n">
-        <v>417515.079155</v>
+        <v>416996.39603</v>
       </c>
       <c r="V41" t="n">
-        <v>434223.305936</v>
+        <v>433666.955776</v>
       </c>
     </row>
     <row r="42">
@@ -3566,58 +3566,58 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8745.55753</v>
+        <v>8759.975697</v>
       </c>
       <c r="F42" t="n">
-        <v>7179.802831</v>
+        <v>7204.524415</v>
       </c>
       <c r="G42" t="n">
-        <v>6206.285096</v>
+        <v>6239.495818</v>
       </c>
       <c r="H42" t="n">
-        <v>5663.770371</v>
+        <v>5704.878232</v>
       </c>
       <c r="I42" t="n">
-        <v>5597.973128</v>
+        <v>5648.863613</v>
       </c>
       <c r="J42" t="n">
-        <v>6057.827276</v>
+        <v>6123.258335</v>
       </c>
       <c r="K42" t="n">
-        <v>6725.937824</v>
+        <v>6809.240003</v>
       </c>
       <c r="L42" t="n">
-        <v>7228.178656</v>
+        <v>7328.585712</v>
       </c>
       <c r="M42" t="n">
-        <v>7786.327552</v>
+        <v>7905.90032</v>
       </c>
       <c r="N42" t="n">
-        <v>8441.760831</v>
+        <v>8583.289852</v>
       </c>
       <c r="O42" t="n">
-        <v>9108.009013999999</v>
+        <v>9273.082184000001</v>
       </c>
       <c r="P42" t="n">
-        <v>9720.236996</v>
+        <v>9909.296351000001</v>
       </c>
       <c r="Q42" t="n">
-        <v>10308.062785</v>
+        <v>10522.246107</v>
       </c>
       <c r="R42" t="n">
-        <v>10792.044072</v>
+        <v>11030.810564</v>
       </c>
       <c r="S42" t="n">
-        <v>11204.048931</v>
+        <v>11467.323211</v>
       </c>
       <c r="T42" t="n">
-        <v>11529.290188</v>
+        <v>11816.563646</v>
       </c>
       <c r="U42" t="n">
-        <v>11763.004904</v>
+        <v>12073.360869</v>
       </c>
       <c r="V42" t="n">
-        <v>11952.795077</v>
+        <v>12286.693018</v>
       </c>
     </row>
     <row r="43">
@@ -3642,58 +3642,58 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>410826.57883</v>
+        <v>410670.531593</v>
       </c>
       <c r="F43" t="n">
-        <v>477998.245113</v>
+        <v>477682.349993</v>
       </c>
       <c r="G43" t="n">
-        <v>556133.230418</v>
+        <v>555682.334193</v>
       </c>
       <c r="H43" t="n">
-        <v>639029.965877</v>
+        <v>638460.6522</v>
       </c>
       <c r="I43" t="n">
-        <v>777298.8095</v>
+        <v>776555.7805230001</v>
       </c>
       <c r="J43" t="n">
-        <v>1010289.135583</v>
+        <v>1009248.379281</v>
       </c>
       <c r="K43" t="n">
-        <v>1318204.901282</v>
+        <v>1316733.399625</v>
       </c>
       <c r="L43" t="n">
-        <v>1626061.240916</v>
+        <v>1624094.200221</v>
       </c>
       <c r="M43" t="n">
-        <v>1974016.44207</v>
+        <v>1971440.908475</v>
       </c>
       <c r="N43" t="n">
-        <v>2377814.462428</v>
+        <v>2374493.596943</v>
       </c>
       <c r="O43" t="n">
-        <v>2821721.462882</v>
+        <v>2817536.269159</v>
       </c>
       <c r="P43" t="n">
-        <v>3286215.689759</v>
+        <v>3281079.603524</v>
       </c>
       <c r="Q43" t="n">
-        <v>3780544.11496</v>
+        <v>3774356.087373</v>
       </c>
       <c r="R43" t="n">
-        <v>4279004.271018</v>
+        <v>4271699.267123</v>
       </c>
       <c r="S43" t="n">
-        <v>4789235.561643</v>
+        <v>4780726.018672</v>
       </c>
       <c r="T43" t="n">
-        <v>5323940.216754</v>
+        <v>5314103.119641</v>
       </c>
       <c r="U43" t="n">
-        <v>5884371.202325</v>
+        <v>5873053.341555</v>
       </c>
       <c r="V43" t="n">
-        <v>6483454.691172</v>
+        <v>6470444.538345</v>
       </c>
     </row>
     <row r="44">
@@ -3718,58 +3718,58 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>186308.533215</v>
+        <v>186350.526232</v>
       </c>
       <c r="F44" t="n">
-        <v>174855.805486</v>
+        <v>174941.143603</v>
       </c>
       <c r="G44" t="n">
-        <v>177963.505317</v>
+        <v>178102.08388</v>
       </c>
       <c r="H44" t="n">
-        <v>191969.44046</v>
+        <v>192169.093523</v>
       </c>
       <c r="I44" t="n">
-        <v>220103.440918</v>
+        <v>220379.225075</v>
       </c>
       <c r="J44" t="n">
-        <v>267363.40104</v>
+        <v>267745.564842</v>
       </c>
       <c r="K44" t="n">
-        <v>325086.971525</v>
+        <v>325598.680323</v>
       </c>
       <c r="L44" t="n">
-        <v>377400.749783</v>
+        <v>378039.413314</v>
       </c>
       <c r="M44" t="n">
-        <v>435034.207742</v>
+        <v>435815.058117</v>
       </c>
       <c r="N44" t="n">
-        <v>499203.834925</v>
+        <v>500147.713954</v>
       </c>
       <c r="O44" t="n">
-        <v>565770.239253</v>
+        <v>566894.173799</v>
       </c>
       <c r="P44" t="n">
-        <v>632484.997075</v>
+        <v>633802.6848329999</v>
       </c>
       <c r="Q44" t="n">
-        <v>702790.992793</v>
+        <v>704320.2357739999</v>
       </c>
       <c r="R44" t="n">
-        <v>772519.053498</v>
+        <v>774266.114482</v>
       </c>
       <c r="S44" t="n">
-        <v>845441.79232</v>
+        <v>847418.923988</v>
       </c>
       <c r="T44" t="n">
-        <v>920446.576278</v>
+        <v>922663.41175</v>
       </c>
       <c r="U44" t="n">
-        <v>996509.970217</v>
+        <v>998971.433968</v>
       </c>
       <c r="V44" t="n">
-        <v>1076531.248912</v>
+        <v>1079252.356799</v>
       </c>
     </row>
     <row r="45">
@@ -3794,58 +3794,58 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37711.756304</v>
+        <v>37727.597863</v>
       </c>
       <c r="F45" t="n">
-        <v>34379.165732</v>
+        <v>34408.243551</v>
       </c>
       <c r="G45" t="n">
-        <v>32197.840583</v>
+        <v>32240.681103</v>
       </c>
       <c r="H45" t="n">
-        <v>31339.411583</v>
+        <v>31396.522907</v>
       </c>
       <c r="I45" t="n">
-        <v>32748.906296</v>
+        <v>32823.230616</v>
       </c>
       <c r="J45" t="n">
-        <v>37266.812706</v>
+        <v>37365.305101</v>
       </c>
       <c r="K45" t="n">
-        <v>43534.531828</v>
+        <v>43662.059865</v>
       </c>
       <c r="L45" t="n">
-        <v>49442.266277</v>
+        <v>49597.715062</v>
       </c>
       <c r="M45" t="n">
-        <v>56137.811416</v>
+        <v>56324.436606</v>
       </c>
       <c r="N45" t="n">
-        <v>63934.404867</v>
+        <v>64156.872138</v>
       </c>
       <c r="O45" t="n">
-        <v>72420.222343</v>
+        <v>72681.618403</v>
       </c>
       <c r="P45" t="n">
-        <v>81291.04927800001</v>
+        <v>81593.374398</v>
       </c>
       <c r="Q45" t="n">
-        <v>90708.075662</v>
+        <v>91054.754917</v>
       </c>
       <c r="R45" t="n">
-        <v>99733.382358</v>
+        <v>100125.214253</v>
       </c>
       <c r="S45" t="n">
-        <v>108388.539253</v>
+        <v>108827.336856</v>
       </c>
       <c r="T45" t="n">
-        <v>116264.315605</v>
+        <v>116751.416197</v>
       </c>
       <c r="U45" t="n">
-        <v>123099.707404</v>
+        <v>123635.810032</v>
       </c>
       <c r="V45" t="n">
-        <v>129189.422661</v>
+        <v>129777.150125</v>
       </c>
     </row>
     <row r="46">
@@ -3870,58 +3870,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>127085.850076</v>
+        <v>127127.298682</v>
       </c>
       <c r="F46" t="n">
-        <v>122848.716715</v>
+        <v>122932.220963</v>
       </c>
       <c r="G46" t="n">
-        <v>128563.25299</v>
+        <v>128698.401191</v>
       </c>
       <c r="H46" t="n">
-        <v>141259.855619</v>
+        <v>141457.868604</v>
       </c>
       <c r="I46" t="n">
-        <v>164385.871088</v>
+        <v>164668.502142</v>
       </c>
       <c r="J46" t="n">
-        <v>206192.477956</v>
+        <v>206601.412656</v>
       </c>
       <c r="K46" t="n">
-        <v>262316.7491</v>
+        <v>262892.325278</v>
       </c>
       <c r="L46" t="n">
-        <v>322093.823484</v>
+        <v>322852.019494</v>
       </c>
       <c r="M46" t="n">
-        <v>394730.716572</v>
+        <v>395705.017654</v>
       </c>
       <c r="N46" t="n">
-        <v>481971.083972</v>
+        <v>483204.100192</v>
       </c>
       <c r="O46" t="n">
-        <v>581086.0113979999</v>
+        <v>582619.017825</v>
       </c>
       <c r="P46" t="n">
-        <v>691174.990348</v>
+        <v>693045.520651</v>
       </c>
       <c r="Q46" t="n">
-        <v>817787.30959</v>
+        <v>820041.964794</v>
       </c>
       <c r="R46" t="n">
-        <v>956343.159253</v>
+        <v>959009.5150360001</v>
       </c>
       <c r="S46" t="n">
-        <v>1109674.852708</v>
+        <v>1112788.137541</v>
       </c>
       <c r="T46" t="n">
-        <v>1274813.008252</v>
+        <v>1278404.677321</v>
       </c>
       <c r="U46" t="n">
-        <v>1448589.144064</v>
+        <v>1452687.61421</v>
       </c>
       <c r="V46" t="n">
-        <v>1634011.815758</v>
+        <v>1638657.977841</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1588615.016777</v>
+        <v>1589671.390076</v>
       </c>
       <c r="F47" t="n">
-        <v>1604123.681129</v>
+        <v>1606056.394684</v>
       </c>
       <c r="G47" t="n">
-        <v>1596874.857924</v>
+        <v>1599725.251275</v>
       </c>
       <c r="H47" t="n">
-        <v>1637613.008079</v>
+        <v>1641472.806968</v>
       </c>
       <c r="I47" t="n">
-        <v>1804026.035169</v>
+        <v>1809191.545482</v>
       </c>
       <c r="J47" t="n">
-        <v>2172605.868094</v>
+        <v>2179714.008954</v>
       </c>
       <c r="K47" t="n">
-        <v>2676816.374911</v>
+        <v>2686428.171148</v>
       </c>
       <c r="L47" t="n">
-        <v>3182338.647875</v>
+        <v>3194591.689868</v>
       </c>
       <c r="M47" t="n">
-        <v>3754996.749324</v>
+        <v>3770297.056602</v>
       </c>
       <c r="N47" t="n">
-        <v>4380872.49857</v>
+        <v>4399736.375169</v>
       </c>
       <c r="O47" t="n">
-        <v>4999389.714172</v>
+        <v>5022233.381895</v>
       </c>
       <c r="P47" t="n">
-        <v>5562244.719571</v>
+        <v>5589360.714771</v>
       </c>
       <c r="Q47" t="n">
-        <v>6085047.422597</v>
+        <v>6116822.278546</v>
       </c>
       <c r="R47" t="n">
-        <v>6523783.378805</v>
+        <v>6560378.391027</v>
       </c>
       <c r="S47" t="n">
-        <v>6901355.578968</v>
+        <v>6943006.247277</v>
       </c>
       <c r="T47" t="n">
-        <v>7202943.564775</v>
+        <v>7249788.829408</v>
       </c>
       <c r="U47" t="n">
-        <v>7436233.61886</v>
+        <v>7488425.01713</v>
       </c>
       <c r="V47" t="n">
-        <v>7637393.713021</v>
+        <v>7695294.621209</v>
       </c>
     </row>
     <row r="48">
@@ -4022,58 +4022,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>93733.58712700001</v>
+        <v>93804.00337000001</v>
       </c>
       <c r="F48" t="n">
-        <v>82117.14378699999</v>
+        <v>82242.938154</v>
       </c>
       <c r="G48" t="n">
-        <v>75627.00316199999</v>
+        <v>75804.879602</v>
       </c>
       <c r="H48" t="n">
-        <v>72529.850928</v>
+        <v>72759.671884</v>
       </c>
       <c r="I48" t="n">
-        <v>74603.08384799999</v>
+        <v>74896.70745099999</v>
       </c>
       <c r="J48" t="n">
-        <v>83307.805859</v>
+        <v>83693.24061399999</v>
       </c>
       <c r="K48" t="n">
-        <v>95285.27742499999</v>
+        <v>95783.028812</v>
       </c>
       <c r="L48" t="n">
-        <v>106153.828713</v>
+        <v>106761.095072</v>
       </c>
       <c r="M48" t="n">
-        <v>119218.479808</v>
+        <v>119949.870053</v>
       </c>
       <c r="N48" t="n">
-        <v>134799.094649</v>
+        <v>135674.345697</v>
       </c>
       <c r="O48" t="n">
-        <v>151957.798855</v>
+        <v>152993.168017</v>
       </c>
       <c r="P48" t="n">
-        <v>170138.631155</v>
+        <v>171346.301302</v>
       </c>
       <c r="Q48" t="n">
-        <v>190259.106778</v>
+        <v>191657.441464</v>
       </c>
       <c r="R48" t="n">
-        <v>211205.88021</v>
+        <v>212805.583517</v>
       </c>
       <c r="S48" t="n">
-        <v>233679.215119</v>
+        <v>235495.985825</v>
       </c>
       <c r="T48" t="n">
-        <v>256978.192206</v>
+        <v>259025.279406</v>
       </c>
       <c r="U48" t="n">
-        <v>280453.708043</v>
+        <v>282743.272371</v>
       </c>
       <c r="V48" t="n">
-        <v>304352.292232</v>
+        <v>306905.333884</v>
       </c>
     </row>
     <row r="49">
@@ -4098,58 +4098,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>557307.156036</v>
+        <v>557108.384415</v>
       </c>
       <c r="F49" t="n">
-        <v>514457.170219</v>
+        <v>514144.812523</v>
       </c>
       <c r="G49" t="n">
-        <v>481354.465244</v>
+        <v>481007.313589</v>
       </c>
       <c r="H49" t="n">
-        <v>463172.368702</v>
+        <v>462818.46723</v>
       </c>
       <c r="I49" t="n">
-        <v>475928.059353</v>
+        <v>475552.21903</v>
       </c>
       <c r="J49" t="n">
-        <v>534191.667501</v>
+        <v>533750.415208</v>
       </c>
       <c r="K49" t="n">
-        <v>616874.754062</v>
+        <v>616333.005755</v>
       </c>
       <c r="L49" t="n">
-        <v>695815.9845509999</v>
+        <v>695159.137644</v>
       </c>
       <c r="M49" t="n">
-        <v>792548.192771</v>
+        <v>791742.295229</v>
       </c>
       <c r="N49" t="n">
-        <v>910988.271801</v>
+        <v>909994.539267</v>
       </c>
       <c r="O49" t="n">
-        <v>1042217.829652</v>
+        <v>1041005.9043</v>
       </c>
       <c r="P49" t="n">
-        <v>1178930.417941</v>
+        <v>1177479.917538</v>
       </c>
       <c r="Q49" t="n">
-        <v>1325107.318638</v>
+        <v>1323392.979002</v>
       </c>
       <c r="R49" t="n">
-        <v>1479323.954209</v>
+        <v>1477317.047347</v>
       </c>
       <c r="S49" t="n">
-        <v>1648262.886119</v>
+        <v>1645919.648801</v>
       </c>
       <c r="T49" t="n">
-        <v>1827232.664141</v>
+        <v>1824512.122298</v>
       </c>
       <c r="U49" t="n">
-        <v>2008779.770398</v>
+        <v>2005646.600129</v>
       </c>
       <c r="V49" t="n">
-        <v>2193529.872631</v>
+        <v>2189940.971117</v>
       </c>
     </row>
     <row r="50">
@@ -4174,58 +4174,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14884.687417</v>
+        <v>14879.723415</v>
       </c>
       <c r="F50" t="n">
-        <v>12541.686549</v>
+        <v>12534.665851</v>
       </c>
       <c r="G50" t="n">
-        <v>10425.457261</v>
+        <v>10418.759004</v>
       </c>
       <c r="H50" t="n">
-        <v>8952.406472999999</v>
+        <v>8946.598980000001</v>
       </c>
       <c r="I50" t="n">
-        <v>8314.131952</v>
+        <v>8308.840784</v>
       </c>
       <c r="J50" t="n">
-        <v>8522.110062</v>
+        <v>8516.691407</v>
       </c>
       <c r="K50" t="n">
-        <v>9030.608108</v>
+        <v>9024.723035000001</v>
       </c>
       <c r="L50" t="n">
-        <v>9387.722873999999</v>
+        <v>9381.315132</v>
       </c>
       <c r="M50" t="n">
-        <v>9949.532982999999</v>
+        <v>9942.318335</v>
       </c>
       <c r="N50" t="n">
-        <v>10709.520121</v>
+        <v>10701.244586</v>
       </c>
       <c r="O50" t="n">
-        <v>11574.52158</v>
+        <v>11565.027816</v>
       </c>
       <c r="P50" t="n">
-        <v>12496.987012</v>
+        <v>12486.161793</v>
       </c>
       <c r="Q50" t="n">
-        <v>13570.514035</v>
+        <v>13558.134826</v>
       </c>
       <c r="R50" t="n">
-        <v>14718.480311</v>
+        <v>14704.354315</v>
       </c>
       <c r="S50" t="n">
-        <v>16005.3611</v>
+        <v>15989.194416</v>
       </c>
       <c r="T50" t="n">
-        <v>17381.052958</v>
+        <v>17362.580329</v>
       </c>
       <c r="U50" t="n">
-        <v>18804.465846</v>
+        <v>18783.424861</v>
       </c>
       <c r="V50" t="n">
-        <v>20323.257685</v>
+        <v>20299.266957</v>
       </c>
     </row>
     <row r="51">
@@ -4250,58 +4250,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>148349.192356</v>
+        <v>148382.809424</v>
       </c>
       <c r="F51" t="n">
-        <v>122861.293884</v>
+        <v>122932.66208</v>
       </c>
       <c r="G51" t="n">
-        <v>108647.182012</v>
+        <v>108762.665273</v>
       </c>
       <c r="H51" t="n">
-        <v>102160.315688</v>
+        <v>102322.479126</v>
       </c>
       <c r="I51" t="n">
-        <v>104986.994191</v>
+        <v>105204.981005</v>
       </c>
       <c r="J51" t="n">
-        <v>118667.122521</v>
+        <v>118963.014595</v>
       </c>
       <c r="K51" t="n">
-        <v>137873.07358</v>
+        <v>138264.729037</v>
       </c>
       <c r="L51" t="n">
-        <v>156098.161082</v>
+        <v>156585.636026</v>
       </c>
       <c r="M51" t="n">
-        <v>178587.898558</v>
+        <v>179185.466597</v>
       </c>
       <c r="N51" t="n">
-        <v>206310.289723</v>
+        <v>207035.794345</v>
       </c>
       <c r="O51" t="n">
-        <v>237674.466758</v>
+        <v>238541.151332</v>
       </c>
       <c r="P51" t="n">
-        <v>271525.811286</v>
+        <v>272544.325109</v>
       </c>
       <c r="Q51" t="n">
-        <v>309280.864144</v>
+        <v>310467.665803</v>
       </c>
       <c r="R51" t="n">
-        <v>348370.904427</v>
+        <v>349732.389012</v>
       </c>
       <c r="S51" t="n">
-        <v>389928.974042</v>
+        <v>391476.835592</v>
       </c>
       <c r="T51" t="n">
-        <v>432990.099694</v>
+        <v>434732.322872</v>
       </c>
       <c r="U51" t="n">
-        <v>477035.613297</v>
+        <v>478978.907162</v>
       </c>
       <c r="V51" t="n">
-        <v>523071.016336</v>
+        <v>525229.152486</v>
       </c>
     </row>
     <row r="52">
@@ -4326,58 +4326,58 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>153393.105814</v>
+        <v>153363.701516</v>
       </c>
       <c r="F52" t="n">
-        <v>113809.626742</v>
+        <v>113782.376498</v>
       </c>
       <c r="G52" t="n">
-        <v>90581.669993</v>
+        <v>90569.977938</v>
       </c>
       <c r="H52" t="n">
-        <v>79878.582654</v>
+        <v>79881.725209</v>
       </c>
       <c r="I52" t="n">
-        <v>78984.22229000001</v>
+        <v>78999.73321400001</v>
       </c>
       <c r="J52" t="n">
-        <v>89214.70643400001</v>
+        <v>89240.631932</v>
       </c>
       <c r="K52" t="n">
-        <v>104968.829379</v>
+        <v>105003.734112</v>
       </c>
       <c r="L52" t="n">
-        <v>119724.420894</v>
+        <v>119765.768092</v>
       </c>
       <c r="M52" t="n">
-        <v>135708.706774</v>
+        <v>135756.166652</v>
       </c>
       <c r="N52" t="n">
-        <v>153577.739845</v>
+        <v>153631.540014</v>
       </c>
       <c r="O52" t="n">
-        <v>172647.551893</v>
+        <v>172707.295348</v>
       </c>
       <c r="P52" t="n">
-        <v>192802.196782</v>
+        <v>192866.862189</v>
       </c>
       <c r="Q52" t="n">
-        <v>215681.590346</v>
+        <v>215749.454996</v>
       </c>
       <c r="R52" t="n">
-        <v>240377.179477</v>
+        <v>240444.932538</v>
       </c>
       <c r="S52" t="n">
-        <v>268359.411077</v>
+        <v>268422.791016</v>
       </c>
       <c r="T52" t="n">
-        <v>299801.805518</v>
+        <v>299855.072007</v>
       </c>
       <c r="U52" t="n">
-        <v>335188.027752</v>
+        <v>335223.186084</v>
       </c>
       <c r="V52" t="n">
-        <v>375949.508726</v>
+        <v>375956.216387</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>251795.690908</v>
+        <v>251795.685278</v>
       </c>
       <c r="F54" t="n">
-        <v>327271.505945</v>
+        <v>327271.48516</v>
       </c>
       <c r="G54" t="n">
-        <v>437183.49957</v>
+        <v>437183.436087</v>
       </c>
       <c r="H54" t="n">
-        <v>560706.407438</v>
+        <v>560706.222027</v>
       </c>
       <c r="I54" t="n">
-        <v>721207.975556</v>
+        <v>721207.283094</v>
       </c>
       <c r="J54" t="n">
         <v>1725473.137064</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>255115.663692</v>
+        <v>255115.669322</v>
       </c>
       <c r="F55" t="n">
-        <v>308916.316596</v>
+        <v>308916.337381</v>
       </c>
       <c r="G55" t="n">
-        <v>390914.847403</v>
+        <v>390914.910886</v>
       </c>
       <c r="H55" t="n">
-        <v>481957.729364</v>
+        <v>481957.914774</v>
       </c>
       <c r="I55" t="n">
-        <v>602594.9620000001</v>
+        <v>602595.654463</v>
       </c>
       <c r="J55" t="n">
         <v>93856.567177</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5.907642</v>
+        <v>5.430461</v>
       </c>
       <c r="F58" t="n">
-        <v>15.604614</v>
+        <v>14.344851</v>
       </c>
       <c r="G58" t="n">
-        <v>38.034584</v>
+        <v>34.966616</v>
       </c>
       <c r="H58" t="n">
-        <v>92.69925499999999</v>
+        <v>85.233921</v>
       </c>
       <c r="I58" t="n">
-        <v>280.782496</v>
+        <v>258.276818</v>
       </c>
       <c r="J58" t="n">
         <v>41234.378678</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.582513</v>
+        <v>1.454687</v>
       </c>
       <c r="F59" t="n">
-        <v>4.33913</v>
+        <v>3.988831</v>
       </c>
       <c r="G59" t="n">
-        <v>10.939763</v>
+        <v>10.057333</v>
       </c>
       <c r="H59" t="n">
-        <v>26.853196</v>
+        <v>24.690632</v>
       </c>
       <c r="I59" t="n">
-        <v>81.246088</v>
+        <v>74.733936</v>
       </c>
       <c r="J59" t="n">
         <v>11893.817409</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.117696</v>
+        <v>2.865868</v>
       </c>
       <c r="F60" t="n">
-        <v>6.621694</v>
+        <v>6.087124</v>
       </c>
       <c r="G60" t="n">
-        <v>13.179983</v>
+        <v>12.116852</v>
       </c>
       <c r="H60" t="n">
-        <v>27.908926</v>
+        <v>25.661341</v>
       </c>
       <c r="I60" t="n">
-        <v>77.60520699999999</v>
+        <v>71.384884</v>
       </c>
       <c r="J60" t="n">
         <v>10897.585448</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>97208.467133</v>
+        <v>97209.039253</v>
       </c>
       <c r="F61" t="n">
-        <v>103326.538092</v>
+        <v>103327.848245</v>
       </c>
       <c r="G61" t="n">
-        <v>121520.412097</v>
+        <v>121522.687756</v>
       </c>
       <c r="H61" t="n">
-        <v>142531.467919</v>
+        <v>142535.01618</v>
       </c>
       <c r="I61" t="n">
-        <v>168468.646767</v>
+        <v>168474.416141</v>
       </c>
       <c r="J61" t="n">
         <v>203638.980495</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>55530.227429</v>
+        <v>55525.332362</v>
       </c>
       <c r="F62" t="n">
-        <v>61741.055069</v>
+        <v>61727.214934</v>
       </c>
       <c r="G62" t="n">
-        <v>73873.003312</v>
+        <v>73839.295082</v>
       </c>
       <c r="H62" t="n">
-        <v>85769.273239</v>
+        <v>85690.201247</v>
       </c>
       <c r="I62" t="n">
-        <v>99108.748422</v>
+        <v>98882.77257299999</v>
       </c>
       <c r="J62" t="n">
         <v>501213.502029</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>34209.605082</v>
+        <v>34205.54947</v>
       </c>
       <c r="F63" t="n">
-        <v>37589.644231</v>
+        <v>37578.398782</v>
       </c>
       <c r="G63" t="n">
-        <v>44245.246883</v>
+        <v>44218.553057</v>
       </c>
       <c r="H63" t="n">
-        <v>51951.815096</v>
+        <v>51888.999807</v>
       </c>
       <c r="I63" t="n">
-        <v>63509.770909</v>
+        <v>63321.476379</v>
       </c>
       <c r="J63" t="n">
         <v>427781.530596</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.6661049999999999</v>
+        <v>0.612302</v>
       </c>
       <c r="F64" t="n">
-        <v>1.607612</v>
+        <v>1.47783</v>
       </c>
       <c r="G64" t="n">
-        <v>3.686708</v>
+        <v>3.389329</v>
       </c>
       <c r="H64" t="n">
-        <v>8.657359</v>
+        <v>7.960157</v>
       </c>
       <c r="I64" t="n">
-        <v>25.723664</v>
+        <v>23.661824</v>
       </c>
       <c r="J64" t="n">
         <v>3723.057737</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>295526.520174</v>
+        <v>295531.642481</v>
       </c>
       <c r="F65" t="n">
-        <v>337689.91064</v>
+        <v>337703.853488</v>
       </c>
       <c r="G65" t="n">
-        <v>430155.453157</v>
+        <v>430188.06309</v>
       </c>
       <c r="H65" t="n">
-        <v>541987.018638</v>
+        <v>542062.1989</v>
       </c>
       <c r="I65" t="n">
-        <v>681623.860287</v>
+        <v>681839.721929</v>
       </c>
       <c r="J65" t="n">
         <v>504797.48656</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>104374.204348</v>
+        <v>104376.268359</v>
       </c>
       <c r="F66" t="n">
-        <v>117666.004966</v>
+        <v>117671.584762</v>
       </c>
       <c r="G66" t="n">
-        <v>148385.761884</v>
+        <v>148398.835407</v>
       </c>
       <c r="H66" t="n">
-        <v>185144.573414</v>
+        <v>185174.813904</v>
       </c>
       <c r="I66" t="n">
-        <v>230634.727954</v>
+        <v>230721.94032</v>
       </c>
       <c r="J66" t="n">
         <v>142854.36577</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123829.512935</v>
+        <v>123832.924841</v>
       </c>
       <c r="F67" t="n">
-        <v>143237.52652</v>
+        <v>143247.113952</v>
       </c>
       <c r="G67" t="n">
-        <v>192019.879379</v>
+        <v>192044.305952</v>
       </c>
       <c r="H67" t="n">
-        <v>255965.789198</v>
+        <v>256027.642744</v>
       </c>
       <c r="I67" t="n">
-        <v>337622.793785</v>
+        <v>337816.534523</v>
       </c>
       <c r="J67" t="n">
         <v>89424.371409</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10363.776489</v>
+        <v>10362.979267</v>
       </c>
       <c r="F68" t="n">
-        <v>11881.903701</v>
+        <v>11879.574404</v>
       </c>
       <c r="G68" t="n">
-        <v>15998.168757</v>
+        <v>15991.730042</v>
       </c>
       <c r="H68" t="n">
-        <v>20909.719743</v>
+        <v>20892.572596</v>
       </c>
       <c r="I68" t="n">
-        <v>26481.44593</v>
+        <v>26427.334999</v>
       </c>
       <c r="J68" t="n">
         <v>131575.555116</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.350916</v>
+        <v>1.241797</v>
       </c>
       <c r="F69" t="n">
-        <v>3.52122</v>
+        <v>3.236951</v>
       </c>
       <c r="G69" t="n">
-        <v>8.268326</v>
+        <v>7.601381</v>
       </c>
       <c r="H69" t="n">
-        <v>19.34635</v>
+        <v>17.788334</v>
       </c>
       <c r="I69" t="n">
-        <v>56.80658</v>
+        <v>52.253338</v>
       </c>
       <c r="J69" t="n">
         <v>8234.208613999999</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>78751.552759</v>
+        <v>78753.565143</v>
       </c>
       <c r="F70" t="n">
-        <v>85334.584005</v>
+        <v>85339.87019099999</v>
       </c>
       <c r="G70" t="n">
-        <v>105449.487671</v>
+        <v>105461.853895</v>
       </c>
       <c r="H70" t="n">
-        <v>130448.052235</v>
+        <v>130476.989781</v>
       </c>
       <c r="I70" t="n">
-        <v>162370.814261</v>
+        <v>162455.960672</v>
       </c>
       <c r="J70" t="n">
         <v>56213.282657</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33562.273636</v>
+        <v>33561.336139</v>
       </c>
       <c r="F71" t="n">
-        <v>39279.450948</v>
+        <v>39276.596086</v>
       </c>
       <c r="G71" t="n">
-        <v>47857.711003</v>
+        <v>47850.417157</v>
       </c>
       <c r="H71" t="n">
-        <v>56497.954194</v>
+        <v>56480.073191</v>
       </c>
       <c r="I71" t="n">
-        <v>66443.25463900001</v>
+        <v>66389.618298</v>
       </c>
       <c r="J71" t="n">
         <v>179712.560883</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>70669.680471</v>
+        <v>70670.25986000001</v>
       </c>
       <c r="F72" t="n">
-        <v>70565.33603400001</v>
+        <v>70566.642205</v>
       </c>
       <c r="G72" t="n">
-        <v>80806.75719800001</v>
+        <v>80809.202172</v>
       </c>
       <c r="H72" t="n">
-        <v>93976.79644999999</v>
+        <v>93981.25593100001</v>
       </c>
       <c r="I72" t="n">
-        <v>111540.340403</v>
+        <v>111550.242291</v>
       </c>
       <c r="J72" t="n">
         <v>124811.06751</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>546.96586</v>
+        <v>544.9550840000001</v>
       </c>
       <c r="F73" t="n">
-        <v>473.544853</v>
+        <v>469.499316</v>
       </c>
       <c r="G73" t="n">
-        <v>440.977623</v>
+        <v>434.231054</v>
       </c>
       <c r="H73" t="n">
-        <v>485.022531</v>
+        <v>472.629715</v>
       </c>
       <c r="I73" t="n">
-        <v>734.161756</v>
+        <v>702.62413</v>
       </c>
       <c r="J73" t="n">
         <v>53175.846607</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.571814</v>
+        <v>0.525626</v>
       </c>
       <c r="F74" t="n">
-        <v>1.71712</v>
+        <v>1.578497</v>
       </c>
       <c r="G74" t="n">
-        <v>4.18838</v>
+        <v>3.850534</v>
       </c>
       <c r="H74" t="n">
-        <v>9.693428000000001</v>
+        <v>8.912789</v>
       </c>
       <c r="I74" t="n">
-        <v>27.745621</v>
+        <v>25.521714</v>
       </c>
       <c r="J74" t="n">
         <v>3901.713185</v>
@@ -6074,58 +6074,58 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>12297.011806</v>
+        <v>12297.010529</v>
       </c>
       <c r="F75" t="n">
-        <v>13652.016388</v>
+        <v>13652.013821</v>
       </c>
       <c r="G75" t="n">
-        <v>17572.700975</v>
+        <v>17572.698662</v>
       </c>
       <c r="H75" t="n">
-        <v>22007.085143</v>
+        <v>22007.084438</v>
       </c>
       <c r="I75" t="n">
-        <v>27072.086042</v>
+        <v>27072.087532</v>
       </c>
       <c r="J75" t="n">
-        <v>35352.38398</v>
+        <v>35352.388151</v>
       </c>
       <c r="K75" t="n">
-        <v>47860.098097</v>
+        <v>47860.105826</v>
       </c>
       <c r="L75" t="n">
-        <v>57458.408231</v>
+        <v>57458.418837</v>
       </c>
       <c r="M75" t="n">
-        <v>63505.367747</v>
+        <v>63505.380745</v>
       </c>
       <c r="N75" t="n">
-        <v>68805.27100399999</v>
+        <v>68805.286825</v>
       </c>
       <c r="O75" t="n">
-        <v>75434.40274400001</v>
+        <v>75434.42531799999</v>
       </c>
       <c r="P75" t="n">
-        <v>81546.845456</v>
+        <v>81546.881524</v>
       </c>
       <c r="Q75" t="n">
-        <v>86144.200635</v>
+        <v>86144.260144</v>
       </c>
       <c r="R75" t="n">
-        <v>92660.22277199999</v>
+        <v>92660.321686</v>
       </c>
       <c r="S75" t="n">
-        <v>100690.894087</v>
+        <v>100691.054292</v>
       </c>
       <c r="T75" t="n">
-        <v>109098.967666</v>
+        <v>109099.218558</v>
       </c>
       <c r="U75" t="n">
-        <v>117775.71738</v>
+        <v>117776.106535</v>
       </c>
       <c r="V75" t="n">
-        <v>127145.39772</v>
+        <v>127146.017203</v>
       </c>
     </row>
     <row r="76">
@@ -6150,58 +6150,58 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11141.084318</v>
+        <v>11141.098746</v>
       </c>
       <c r="F76" t="n">
-        <v>12789.957572</v>
+        <v>12790.006498</v>
       </c>
       <c r="G76" t="n">
-        <v>13483.231461</v>
+        <v>13483.321323</v>
       </c>
       <c r="H76" t="n">
-        <v>14383.61009</v>
+        <v>14383.74741</v>
       </c>
       <c r="I76" t="n">
-        <v>16346.18861</v>
+        <v>16346.395971</v>
       </c>
       <c r="J76" t="n">
-        <v>21269.963156</v>
+        <v>21270.315427</v>
       </c>
       <c r="K76" t="n">
-        <v>29902.544243</v>
+        <v>29903.186223</v>
       </c>
       <c r="L76" t="n">
-        <v>37996.723672</v>
+        <v>37997.7756</v>
       </c>
       <c r="M76" t="n">
-        <v>44005.189929</v>
+        <v>44006.735066</v>
       </c>
       <c r="N76" t="n">
-        <v>49409.167371</v>
+        <v>49411.343693</v>
       </c>
       <c r="O76" t="n">
-        <v>54752.432357</v>
+        <v>54755.407066</v>
       </c>
       <c r="P76" t="n">
-        <v>58637.742897</v>
+        <v>58641.633235</v>
       </c>
       <c r="Q76" t="n">
-        <v>60389.12374</v>
+        <v>60393.991423</v>
       </c>
       <c r="R76" t="n">
-        <v>62758.978256</v>
+        <v>62765.135318</v>
       </c>
       <c r="S76" t="n">
-        <v>66071.53479400001</v>
+        <v>66079.536016</v>
       </c>
       <c r="T76" t="n">
-        <v>69991.379376</v>
+        <v>70002.106181</v>
       </c>
       <c r="U76" t="n">
-        <v>74557.635721</v>
+        <v>74572.611632</v>
       </c>
       <c r="V76" t="n">
-        <v>79733.46329499999</v>
+        <v>79755.441594</v>
       </c>
     </row>
     <row r="77">
@@ -6226,58 +6226,58 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>48973.787305</v>
+        <v>48973.779168</v>
       </c>
       <c r="F77" t="n">
-        <v>61815.872884</v>
+        <v>61815.850759</v>
       </c>
       <c r="G77" t="n">
-        <v>83497.378545</v>
+        <v>83497.338982</v>
       </c>
       <c r="H77" t="n">
-        <v>101246.436389</v>
+        <v>101246.374655</v>
       </c>
       <c r="I77" t="n">
-        <v>114659.167877</v>
+        <v>114659.073891</v>
       </c>
       <c r="J77" t="n">
-        <v>137116.420234</v>
+        <v>137116.268243</v>
       </c>
       <c r="K77" t="n">
-        <v>173858.55588</v>
+        <v>173858.300692</v>
       </c>
       <c r="L77" t="n">
-        <v>201693.539179</v>
+        <v>201693.155595</v>
       </c>
       <c r="M77" t="n">
-        <v>220319.655245</v>
+        <v>220319.123018</v>
       </c>
       <c r="N77" t="n">
-        <v>238606.776418</v>
+        <v>238606.051569</v>
       </c>
       <c r="O77" t="n">
-        <v>262154.140654</v>
+        <v>262153.150294</v>
       </c>
       <c r="P77" t="n">
-        <v>283778.695114</v>
+        <v>283777.369296</v>
       </c>
       <c r="Q77" t="n">
-        <v>300038.878071</v>
+        <v>300037.14616</v>
       </c>
       <c r="R77" t="n">
-        <v>323381.66802</v>
+        <v>323379.351466</v>
       </c>
       <c r="S77" t="n">
-        <v>352826.632498</v>
+        <v>352823.459798</v>
       </c>
       <c r="T77" t="n">
-        <v>384344.118093</v>
+        <v>384339.695888</v>
       </c>
       <c r="U77" t="n">
-        <v>417076.923176</v>
+        <v>417070.61057</v>
       </c>
       <c r="V77" t="n">
-        <v>451899.869554</v>
+        <v>451890.50657</v>
       </c>
     </row>
     <row r="78">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>36686.381336</v>
+        <v>36686.396225</v>
       </c>
       <c r="F78" t="n">
-        <v>35400.954347</v>
+        <v>35400.991519</v>
       </c>
       <c r="G78" t="n">
-        <v>38694.829893</v>
+        <v>38694.905624</v>
       </c>
       <c r="H78" t="n">
-        <v>43914.386434</v>
+        <v>43914.517228</v>
       </c>
       <c r="I78" t="n">
-        <v>52157.465598</v>
+        <v>52157.678819</v>
       </c>
       <c r="J78" t="n">
-        <v>68700.539705</v>
+        <v>68700.90644599999</v>
       </c>
       <c r="K78" t="n">
-        <v>96278.503509</v>
+        <v>96279.159808</v>
       </c>
       <c r="L78" t="n">
-        <v>120849.932328</v>
+        <v>120850.969377</v>
       </c>
       <c r="M78" t="n">
-        <v>140029.299317</v>
+        <v>140030.804492</v>
       </c>
       <c r="N78" t="n">
-        <v>158947.736415</v>
+        <v>158949.874396</v>
       </c>
       <c r="O78" t="n">
-        <v>181920.010386</v>
+        <v>181923.085103</v>
       </c>
       <c r="P78" t="n">
-        <v>204385.134596</v>
+        <v>204389.496384</v>
       </c>
       <c r="Q78" t="n">
-        <v>223453.147171</v>
+        <v>223459.205706</v>
       </c>
       <c r="R78" t="n">
-        <v>247832.347583</v>
+        <v>247840.951447</v>
       </c>
       <c r="S78" t="n">
-        <v>276671.443465</v>
+        <v>276683.863695</v>
       </c>
       <c r="T78" t="n">
-        <v>306560.030128</v>
+        <v>306578.096171</v>
       </c>
       <c r="U78" t="n">
-        <v>336416.148878</v>
+        <v>336442.79109</v>
       </c>
       <c r="V78" t="n">
-        <v>366609.283395</v>
+        <v>366649.782574</v>
       </c>
     </row>
     <row r="79">
@@ -6378,58 +6378,58 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>41005.475303</v>
+        <v>41005.467587</v>
       </c>
       <c r="F79" t="n">
-        <v>59884.511514</v>
+        <v>59884.485915</v>
       </c>
       <c r="G79" t="n">
-        <v>101610.064348</v>
+        <v>101610.002042</v>
       </c>
       <c r="H79" t="n">
-        <v>158090.13536</v>
+        <v>158090.007115</v>
       </c>
       <c r="I79" t="n">
-        <v>226518.398906</v>
+        <v>226518.159906</v>
       </c>
       <c r="J79" t="n">
-        <v>327003.046439</v>
+        <v>327002.601392</v>
       </c>
       <c r="K79" t="n">
-        <v>473822.893636</v>
+        <v>473822.068204</v>
       </c>
       <c r="L79" t="n">
-        <v>598126.937822</v>
+        <v>598125.609401</v>
       </c>
       <c r="M79" t="n">
-        <v>688117.068818</v>
+        <v>688115.1340580001</v>
       </c>
       <c r="N79" t="n">
-        <v>770977.0492829999</v>
+        <v>770974.315208</v>
       </c>
       <c r="O79" t="n">
-        <v>870507.560737</v>
+        <v>870503.699604</v>
       </c>
       <c r="P79" t="n">
-        <v>967224.664723</v>
+        <v>967219.32618</v>
       </c>
       <c r="Q79" t="n">
-        <v>1048696.654122</v>
+        <v>1048689.459348</v>
       </c>
       <c r="R79" t="n">
-        <v>1156226.095405</v>
+        <v>1156216.189828</v>
       </c>
       <c r="S79" t="n">
-        <v>1285717.667657</v>
+        <v>1285703.755315</v>
       </c>
       <c r="T79" t="n">
-        <v>1420978.518792</v>
+        <v>1420958.734149</v>
       </c>
       <c r="U79" t="n">
-        <v>1558480.253724</v>
+        <v>1558451.570944</v>
       </c>
       <c r="V79" t="n">
-        <v>1701312.792714</v>
+        <v>1701269.752899</v>
       </c>
     </row>
     <row r="80">
@@ -6454,58 +6454,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6828.043658</v>
+        <v>6828.042579</v>
       </c>
       <c r="F80" t="n">
-        <v>6530.42509</v>
+        <v>6530.422697</v>
       </c>
       <c r="G80" t="n">
-        <v>7382.140397</v>
+        <v>7382.136445</v>
       </c>
       <c r="H80" t="n">
-        <v>8910.849682</v>
+        <v>8910.843175</v>
       </c>
       <c r="I80" t="n">
-        <v>11329.128548</v>
+        <v>11329.117542</v>
       </c>
       <c r="J80" t="n">
-        <v>15944.410995</v>
+        <v>15944.390891</v>
       </c>
       <c r="K80" t="n">
-        <v>23815.506127</v>
+        <v>23815.46799</v>
       </c>
       <c r="L80" t="n">
-        <v>31753.486394</v>
+        <v>31753.422539</v>
       </c>
       <c r="M80" t="n">
-        <v>38758.843851</v>
+        <v>38758.746932</v>
       </c>
       <c r="N80" t="n">
-        <v>45822.37602</v>
+        <v>45822.233978</v>
       </c>
       <c r="O80" t="n">
-        <v>54123.143739</v>
+        <v>54122.937239</v>
       </c>
       <c r="P80" t="n">
-        <v>62400.327233</v>
+        <v>62400.035282</v>
       </c>
       <c r="Q80" t="n">
-        <v>69784.602896</v>
+        <v>69784.20230800001</v>
       </c>
       <c r="R80" t="n">
-        <v>78968.264994</v>
+        <v>78967.70556</v>
       </c>
       <c r="S80" t="n">
-        <v>89639.677807</v>
+        <v>89638.88370599999</v>
       </c>
       <c r="T80" t="n">
-        <v>100598.292031</v>
+        <v>100597.154212</v>
       </c>
       <c r="U80" t="n">
-        <v>111418.938518</v>
+        <v>111417.28152</v>
       </c>
       <c r="V80" t="n">
-        <v>122138.250659</v>
+        <v>122135.761082</v>
       </c>
     </row>
     <row r="81">
@@ -6530,58 +6530,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>62597.531512</v>
+        <v>62597.519492</v>
       </c>
       <c r="F81" t="n">
-        <v>94006.84854399999</v>
+        <v>94006.80716500001</v>
       </c>
       <c r="G81" t="n">
-        <v>160464.802265</v>
+        <v>160464.698835</v>
       </c>
       <c r="H81" t="n">
-        <v>249997.776415</v>
+        <v>249997.558692</v>
       </c>
       <c r="I81" t="n">
-        <v>358999.178161</v>
+        <v>358998.765853</v>
       </c>
       <c r="J81" t="n">
-        <v>519450.209945</v>
+        <v>519449.435566</v>
       </c>
       <c r="K81" t="n">
-        <v>753439.839578</v>
+        <v>753438.399376</v>
       </c>
       <c r="L81" t="n">
-        <v>951052.692006</v>
+        <v>951050.376349</v>
       </c>
       <c r="M81" t="n">
-        <v>1093577.44582</v>
+        <v>1093574.080095</v>
       </c>
       <c r="N81" t="n">
-        <v>1224102.016009</v>
+        <v>1224097.272023</v>
       </c>
       <c r="O81" t="n">
-        <v>1381540.404867</v>
+        <v>1381533.712774</v>
       </c>
       <c r="P81" t="n">
-        <v>1537084.633743</v>
+        <v>1537075.367834</v>
       </c>
       <c r="Q81" t="n">
-        <v>1673363.885672</v>
+        <v>1673351.338668</v>
       </c>
       <c r="R81" t="n">
-        <v>1856871.884391</v>
+        <v>1856854.48163</v>
       </c>
       <c r="S81" t="n">
-        <v>2081883.580174</v>
+        <v>2081858.91097</v>
       </c>
       <c r="T81" t="n">
-        <v>2323122.513361</v>
+        <v>2323087.062125</v>
       </c>
       <c r="U81" t="n">
-        <v>2574606.746046</v>
+        <v>2574554.782259</v>
       </c>
       <c r="V81" t="n">
-        <v>2841588.18845</v>
+        <v>2841509.312718</v>
       </c>
     </row>
     <row r="82">
@@ -6606,58 +6606,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>391.571311</v>
+        <v>391.574069</v>
       </c>
       <c r="F82" t="n">
-        <v>439.388365</v>
+        <v>439.397097</v>
       </c>
       <c r="G82" t="n">
-        <v>553.910564</v>
+        <v>553.93225</v>
       </c>
       <c r="H82" t="n">
-        <v>703.901105</v>
+        <v>703.946021</v>
       </c>
       <c r="I82" t="n">
-        <v>899.87925</v>
+        <v>899.9626919999999</v>
       </c>
       <c r="J82" t="n">
-        <v>1236.458703</v>
+        <v>1236.614452</v>
       </c>
       <c r="K82" t="n">
-        <v>1766.947633</v>
+        <v>1767.238366</v>
       </c>
       <c r="L82" t="n">
-        <v>2239.695238</v>
+        <v>2240.166268</v>
       </c>
       <c r="M82" t="n">
-        <v>2602.182709</v>
+        <v>2602.874609</v>
       </c>
       <c r="N82" t="n">
-        <v>2944.307358</v>
+        <v>2945.292488</v>
       </c>
       <c r="O82" t="n">
-        <v>3345.581077</v>
+        <v>3346.987845</v>
       </c>
       <c r="P82" t="n">
-        <v>3727.093003</v>
+        <v>3729.06545</v>
       </c>
       <c r="Q82" t="n">
-        <v>4042.378909</v>
+        <v>4045.082321</v>
       </c>
       <c r="R82" t="n">
-        <v>4455.420985</v>
+        <v>4459.20875</v>
       </c>
       <c r="S82" t="n">
-        <v>4952.613673</v>
+        <v>4958.018404</v>
       </c>
       <c r="T82" t="n">
-        <v>5474.775848</v>
+        <v>5482.560189</v>
       </c>
       <c r="U82" t="n">
-        <v>6012.184295</v>
+        <v>6023.581103</v>
       </c>
       <c r="V82" t="n">
-        <v>6584.019602</v>
+        <v>6601.254871</v>
       </c>
     </row>
     <row r="83">
@@ -6682,58 +6682,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>25308.046451</v>
+        <v>25308.044605</v>
       </c>
       <c r="F83" t="n">
-        <v>37782.34535</v>
+        <v>37782.344582</v>
       </c>
       <c r="G83" t="n">
-        <v>63127.997075</v>
+        <v>63128.021361</v>
       </c>
       <c r="H83" t="n">
-        <v>96011.90854400001</v>
+        <v>96012.010429</v>
       </c>
       <c r="I83" t="n">
-        <v>134219.524476</v>
+        <v>134219.775264</v>
       </c>
       <c r="J83" t="n">
-        <v>189543.660766</v>
+        <v>189544.173354</v>
       </c>
       <c r="K83" t="n">
-        <v>270099.984367</v>
+        <v>270100.946585</v>
       </c>
       <c r="L83" t="n">
-        <v>337771.02913</v>
+        <v>337772.550034</v>
       </c>
       <c r="M83" t="n">
-        <v>386835.623264</v>
+        <v>386837.797684</v>
       </c>
       <c r="N83" t="n">
-        <v>432345.405697</v>
+        <v>432348.435395</v>
       </c>
       <c r="O83" t="n">
-        <v>486651.487725</v>
+        <v>486655.759044</v>
       </c>
       <c r="P83" t="n">
-        <v>538370.557564</v>
+        <v>538376.519145</v>
       </c>
       <c r="Q83" t="n">
-        <v>581080.026673</v>
+        <v>581088.211812</v>
       </c>
       <c r="R83" t="n">
-        <v>637918.406696</v>
+        <v>637929.943414</v>
       </c>
       <c r="S83" t="n">
-        <v>705982.8068960001</v>
+        <v>705999.368854</v>
       </c>
       <c r="T83" t="n">
-        <v>776732.820904</v>
+        <v>776756.788727</v>
       </c>
       <c r="U83" t="n">
-        <v>848324.809722</v>
+        <v>848360.021807</v>
       </c>
       <c r="V83" t="n">
-        <v>922828.773211</v>
+        <v>922882.209088</v>
       </c>
     </row>
     <row r="84">
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>85660.954277</v>
+        <v>85661.207608</v>
       </c>
       <c r="F86" t="n">
-        <v>101476.383014</v>
+        <v>101477.160152</v>
       </c>
       <c r="G86" t="n">
-        <v>109732.606691</v>
+        <v>109734.313613</v>
       </c>
       <c r="H86" t="n">
-        <v>119847.466321</v>
+        <v>119851.226141</v>
       </c>
       <c r="I86" t="n">
-        <v>134587.649952</v>
+        <v>134598.203696</v>
       </c>
       <c r="J86" t="n">
         <v>129025.270051</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6611.74304</v>
+        <v>6611.573895</v>
       </c>
       <c r="F87" t="n">
-        <v>8822.239178</v>
+        <v>8821.666182000001</v>
       </c>
       <c r="G87" t="n">
-        <v>10962.601051</v>
+        <v>10961.153755</v>
       </c>
       <c r="H87" t="n">
-        <v>13465.474926</v>
+        <v>13461.887374</v>
       </c>
       <c r="I87" t="n">
-        <v>16701.638551</v>
+        <v>16690.564479</v>
       </c>
       <c r="J87" t="n">
         <v>61311.106013</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>183057.904912</v>
+        <v>183057.828666</v>
       </c>
       <c r="F88" t="n">
-        <v>194810.467626</v>
+        <v>194810.39125</v>
       </c>
       <c r="G88" t="n">
-        <v>194587.852811</v>
+        <v>194587.867963</v>
       </c>
       <c r="H88" t="n">
-        <v>206120.825743</v>
+        <v>206121.049931</v>
       </c>
       <c r="I88" t="n">
-        <v>232132.880972</v>
+        <v>232133.716856</v>
       </c>
       <c r="J88" t="n">
         <v>285629.377749</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>39962.996003</v>
+        <v>39963.314899</v>
       </c>
       <c r="F89" t="n">
-        <v>45104.783349</v>
+        <v>45105.707693</v>
       </c>
       <c r="G89" t="n">
-        <v>48587.438905</v>
+        <v>48589.457254</v>
       </c>
       <c r="H89" t="n">
-        <v>53116.816961</v>
+        <v>53121.263594</v>
       </c>
       <c r="I89" t="n">
-        <v>59672.083423</v>
+        <v>59684.5875</v>
       </c>
       <c r="J89" t="n">
         <v>31376.145789</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>129239.862745</v>
+        <v>129239.890073</v>
       </c>
       <c r="F90" t="n">
-        <v>148220.918011</v>
+        <v>148221.04319</v>
       </c>
       <c r="G90" t="n">
-        <v>163298.270394</v>
+        <v>163298.556347</v>
       </c>
       <c r="H90" t="n">
-        <v>183684.356238</v>
+        <v>183684.970966</v>
       </c>
       <c r="I90" t="n">
-        <v>211702.143441</v>
+        <v>211703.784286</v>
       </c>
       <c r="J90" t="n">
         <v>256743.336485</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60726.593799</v>
+        <v>60726.892306</v>
       </c>
       <c r="F91" t="n">
-        <v>71852.915094</v>
+        <v>71853.823523</v>
       </c>
       <c r="G91" t="n">
-        <v>78392.739525</v>
+        <v>78394.746573</v>
       </c>
       <c r="H91" t="n">
-        <v>84875.881736</v>
+        <v>84880.264488</v>
       </c>
       <c r="I91" t="n">
-        <v>92935.783329</v>
+        <v>92947.813546</v>
       </c>
       <c r="J91" t="n">
         <v>70807.421757</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65779.670256</v>
+        <v>65780.270886</v>
       </c>
       <c r="F92" t="n">
-        <v>78425.047158</v>
+        <v>78426.87525500001</v>
       </c>
       <c r="G92" t="n">
-        <v>88247.354489</v>
+        <v>88251.50984499999</v>
       </c>
       <c r="H92" t="n">
-        <v>98157.885952</v>
+        <v>98167.184647</v>
       </c>
       <c r="I92" t="n">
-        <v>109958.419734</v>
+        <v>109984.483016</v>
       </c>
       <c r="J92" t="n">
         <v>47309.667797</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>905.034533</v>
+        <v>904.941952</v>
       </c>
       <c r="F93" t="n">
-        <v>1134.58632</v>
+        <v>1134.292815</v>
       </c>
       <c r="G93" t="n">
-        <v>1360.063313</v>
+        <v>1359.352052</v>
       </c>
       <c r="H93" t="n">
-        <v>1665.539269</v>
+        <v>1663.792151</v>
       </c>
       <c r="I93" t="n">
-        <v>2109.521514</v>
+        <v>2104.115809</v>
       </c>
       <c r="J93" t="n">
         <v>21960.1367</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>383974.525882</v>
+        <v>383972.150625</v>
       </c>
       <c r="F94" t="n">
-        <v>481894.478909</v>
+        <v>481886.932841</v>
       </c>
       <c r="G94" t="n">
-        <v>540312.423937</v>
+        <v>540295.3102299999</v>
       </c>
       <c r="H94" t="n">
-        <v>599617.546693</v>
+        <v>599579.40312</v>
       </c>
       <c r="I94" t="n">
-        <v>674764.985062</v>
+        <v>674658.205156</v>
       </c>
       <c r="J94" t="n">
         <v>1163651.946011</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>255640.403056</v>
+        <v>255641.46637</v>
       </c>
       <c r="F95" t="n">
-        <v>326257.164615</v>
+        <v>326260.61013</v>
       </c>
       <c r="G95" t="n">
-        <v>379905.826266</v>
+        <v>379913.840874</v>
       </c>
       <c r="H95" t="n">
-        <v>436867.753198</v>
+        <v>436886.116438</v>
       </c>
       <c r="I95" t="n">
-        <v>506832.881262</v>
+        <v>506885.695002</v>
       </c>
       <c r="J95" t="n">
         <v>450574.925777</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>92853.655659</v>
+        <v>92853.68459400001</v>
       </c>
       <c r="F96" t="n">
-        <v>103366.268057</v>
+        <v>103366.39905</v>
       </c>
       <c r="G96" t="n">
-        <v>103989.074075</v>
+        <v>103989.417112</v>
       </c>
       <c r="H96" t="n">
-        <v>109176.499665</v>
+        <v>109177.320285</v>
       </c>
       <c r="I96" t="n">
-        <v>120973.747984</v>
+        <v>120976.13632</v>
       </c>
       <c r="J96" t="n">
         <v>139650.801226</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>46713.125838</v>
+        <v>46713.248125</v>
       </c>
       <c r="F97" t="n">
-        <v>48032.595821</v>
+        <v>48032.945071</v>
       </c>
       <c r="G97" t="n">
-        <v>46888.881184</v>
+        <v>46889.607022</v>
       </c>
       <c r="H97" t="n">
-        <v>49024.760295</v>
+        <v>49026.327864</v>
       </c>
       <c r="I97" t="n">
-        <v>54904.845309</v>
+        <v>54909.274865</v>
       </c>
       <c r="J97" t="n">
         <v>53165.388216</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>426926.772395</v>
+        <v>426931.672785</v>
       </c>
       <c r="F98" t="n">
-        <v>411332.362654</v>
+        <v>411344.705864</v>
       </c>
       <c r="G98" t="n">
-        <v>454512.490792</v>
+        <v>454541.194003</v>
       </c>
       <c r="H98" t="n">
-        <v>482661.754058</v>
+        <v>482725.462819</v>
       </c>
       <c r="I98" t="n">
-        <v>513052.901594</v>
+        <v>513228.176573</v>
       </c>
       <c r="J98" t="n">
         <v>244640.977136</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>160742.022186</v>
+        <v>160740.159496</v>
       </c>
       <c r="F99" t="n">
-        <v>178976.227549</v>
+        <v>178970.902198</v>
       </c>
       <c r="G99" t="n">
-        <v>231713.717265</v>
+        <v>231699.572778</v>
       </c>
       <c r="H99" t="n">
-        <v>278247.083546</v>
+        <v>278212.548595</v>
       </c>
       <c r="I99" t="n">
-        <v>322721.913543</v>
+        <v>322621.127165</v>
       </c>
       <c r="J99" t="n">
         <v>605223.846714</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>207479.897591</v>
+        <v>207481.930483</v>
       </c>
       <c r="F100" t="n">
-        <v>198570.026397</v>
+        <v>198575.159672</v>
       </c>
       <c r="G100" t="n">
-        <v>223093.598079</v>
+        <v>223105.808536</v>
       </c>
       <c r="H100" t="n">
-        <v>241778.889131</v>
+        <v>241806.666391</v>
       </c>
       <c r="I100" t="n">
-        <v>262084.818772</v>
+        <v>262162.980434</v>
       </c>
       <c r="J100" t="n">
         <v>149941.090478</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>457387.567053</v>
+        <v>457394.88672</v>
       </c>
       <c r="F101" t="n">
-        <v>469102.689389</v>
+        <v>469122.036671</v>
       </c>
       <c r="G101" t="n">
-        <v>558622.488857</v>
+        <v>558670.199639</v>
       </c>
       <c r="H101" t="n">
-        <v>628535.160818</v>
+        <v>628645.956656</v>
       </c>
       <c r="I101" t="n">
-        <v>694538.151875</v>
+        <v>694852.26043</v>
       </c>
       <c r="J101" t="n">
         <v>184992.540974</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>999145.206728</v>
+        <v>999140.096218</v>
       </c>
       <c r="F102" t="n">
-        <v>1085277.617409</v>
+        <v>1085263.720551</v>
       </c>
       <c r="G102" t="n">
-        <v>1384537.160694</v>
+        <v>1384501.551244</v>
       </c>
       <c r="H102" t="n">
-        <v>1659795.24163</v>
+        <v>1659709.726696</v>
       </c>
       <c r="I102" t="n">
-        <v>1938731.752387</v>
+        <v>1938482.865702</v>
       </c>
       <c r="J102" t="n">
         <v>2928691.063072</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1701884.814062</v>
+        <v>1701888.328246</v>
       </c>
       <c r="F103" t="n">
-        <v>1579382.813275</v>
+        <v>1579393.138964</v>
       </c>
       <c r="G103" t="n">
-        <v>1697641.573006</v>
+        <v>1697669.081917</v>
       </c>
       <c r="H103" t="n">
-        <v>1768265.223797</v>
+        <v>1768331.965572</v>
       </c>
       <c r="I103" t="n">
-        <v>1857710.44162</v>
+        <v>1857904.732321</v>
       </c>
       <c r="J103" t="n">
         <v>1738522.677242</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>123648.198516</v>
+        <v>123646.676584</v>
       </c>
       <c r="F104" t="n">
-        <v>129544.518587</v>
+        <v>129540.48988</v>
       </c>
       <c r="G104" t="n">
-        <v>158673.893463</v>
+        <v>158663.908724</v>
       </c>
       <c r="H104" t="n">
-        <v>185819.080045</v>
+        <v>185795.322997</v>
       </c>
       <c r="I104" t="n">
-        <v>214113.651512</v>
+        <v>214044.30502</v>
       </c>
       <c r="J104" t="n">
         <v>409223.025468</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>48830.67748</v>
+        <v>48829.640096</v>
       </c>
       <c r="F105" t="n">
-        <v>51610.878599</v>
+        <v>51608.141408</v>
       </c>
       <c r="G105" t="n">
-        <v>64483.806246</v>
+        <v>64476.925905</v>
       </c>
       <c r="H105" t="n">
-        <v>75817.46515800001</v>
+        <v>75801.21555199999</v>
       </c>
       <c r="I105" t="n">
-        <v>87076.633862</v>
+        <v>87030.03241</v>
       </c>
       <c r="J105" t="n">
         <v>202058.168952</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1145568.391837</v>
+        <v>1145570.54981</v>
       </c>
       <c r="F106" t="n">
-        <v>1255107.845578</v>
+        <v>1255113.856115</v>
       </c>
       <c r="G106" t="n">
-        <v>1628771.640017</v>
+        <v>1628787.33313</v>
       </c>
       <c r="H106" t="n">
-        <v>1963700.28389</v>
+        <v>1963738.995865</v>
       </c>
       <c r="I106" t="n">
-        <v>2281638.486789</v>
+        <v>2281754.878327</v>
       </c>
       <c r="J106" t="n">
         <v>2551259.58967</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>9019.943869000001</v>
+        <v>9019.33618</v>
       </c>
       <c r="F107" t="n">
-        <v>10423.319536</v>
+        <v>10421.521469</v>
       </c>
       <c r="G107" t="n">
-        <v>13282.812456</v>
+        <v>13278.167078</v>
       </c>
       <c r="H107" t="n">
-        <v>15798.669289</v>
+        <v>15787.523842</v>
       </c>
       <c r="I107" t="n">
-        <v>18521.427504</v>
+        <v>18488.699603</v>
       </c>
       <c r="J107" t="n">
         <v>92902.089429</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>156705.897941</v>
+        <v>156699.70559</v>
       </c>
       <c r="F108" t="n">
-        <v>163631.661732</v>
+        <v>163615.319811</v>
       </c>
       <c r="G108" t="n">
-        <v>195824.828186</v>
+        <v>195785.412642</v>
       </c>
       <c r="H108" t="n">
-        <v>221299.420775</v>
+        <v>221209.848195</v>
       </c>
       <c r="I108" t="n">
-        <v>246373.163393</v>
+        <v>246123.677864</v>
       </c>
       <c r="J108" t="n">
         <v>798485.453015</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>216539.246384</v>
+        <v>216541.205601</v>
       </c>
       <c r="F109" t="n">
-        <v>227322.586552</v>
+        <v>227327.915523</v>
       </c>
       <c r="G109" t="n">
-        <v>291428.994492</v>
+        <v>291443.088141</v>
       </c>
       <c r="H109" t="n">
-        <v>360687.196312</v>
+        <v>360722.86183</v>
       </c>
       <c r="I109" t="n">
-        <v>439571.268315</v>
+        <v>439681.482937</v>
       </c>
       <c r="J109" t="n">
         <v>325455.604351</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>830375.889695</v>
+        <v>830388.646788</v>
       </c>
       <c r="F110" t="n">
-        <v>918674.595795</v>
+        <v>918710.869391</v>
       </c>
       <c r="G110" t="n">
-        <v>1189286.999494</v>
+        <v>1189383.949644</v>
       </c>
       <c r="H110" t="n">
-        <v>1428640.518377</v>
+        <v>1428880.39109</v>
       </c>
       <c r="I110" t="n">
-        <v>1653779.874521</v>
+        <v>1654491.503784</v>
       </c>
       <c r="J110" t="n">
         <v>532400.822342</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>723994.239782</v>
+        <v>723992.032157</v>
       </c>
       <c r="F111" t="n">
-        <v>780927.2202400001</v>
+        <v>780921.321473</v>
       </c>
       <c r="G111" t="n">
-        <v>974220.659013</v>
+        <v>974206.2970359999</v>
       </c>
       <c r="H111" t="n">
-        <v>1139218.478279</v>
+        <v>1139185.940997</v>
       </c>
       <c r="I111" t="n">
-        <v>1304969.376291</v>
+        <v>1304879.241767</v>
       </c>
       <c r="J111" t="n">
         <v>1780608.780137</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>597031.734482</v>
+        <v>597015.633247</v>
       </c>
       <c r="F112" t="n">
-        <v>651568.229708</v>
+        <v>651523.494012</v>
       </c>
       <c r="G112" t="n">
-        <v>838580.931837</v>
+        <v>838463.1034810001</v>
       </c>
       <c r="H112" t="n">
-        <v>1011977.97823</v>
+        <v>1011688.016239</v>
       </c>
       <c r="I112" t="n">
-        <v>1188871.111536</v>
+        <v>1188009.009178</v>
       </c>
       <c r="J112" t="n">
         <v>3311509.222228</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>57866.380516</v>
+        <v>57866.595529</v>
       </c>
       <c r="F113" t="n">
-        <v>47611.500363</v>
+        <v>47611.968741</v>
       </c>
       <c r="G113" t="n">
-        <v>48281.204253</v>
+        <v>48282.04788</v>
       </c>
       <c r="H113" t="n">
-        <v>55071.698294</v>
+        <v>55073.306301</v>
       </c>
       <c r="I113" t="n">
-        <v>63760.271259</v>
+        <v>63764.136548</v>
       </c>
       <c r="J113" t="n">
         <v>88806.28873099999</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>28463.388062</v>
+        <v>28463.006108</v>
       </c>
       <c r="F114" t="n">
-        <v>33182.755714</v>
+        <v>33181.555289</v>
       </c>
       <c r="G114" t="n">
-        <v>50451.732172</v>
+        <v>50447.882997</v>
       </c>
       <c r="H114" t="n">
-        <v>75684.190493</v>
+        <v>75672.168704</v>
       </c>
       <c r="I114" t="n">
-        <v>100883.837561</v>
+        <v>100842.421819</v>
       </c>
       <c r="J114" t="n">
         <v>24620.909348</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>114007.397421</v>
+        <v>114007.564364</v>
       </c>
       <c r="F115" t="n">
-        <v>107844.036349</v>
+        <v>107844.768396</v>
       </c>
       <c r="G115" t="n">
-        <v>136939.635167</v>
+        <v>136942.640716</v>
       </c>
       <c r="H115" t="n">
-        <v>184984.993824</v>
+        <v>184995.407606</v>
       </c>
       <c r="I115" t="n">
-        <v>237587.362797</v>
+        <v>237624.91325</v>
       </c>
       <c r="J115" t="n">
         <v>417640.374355</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25216.690023</v>
+        <v>25216.604847</v>
       </c>
       <c r="F116" t="n">
-        <v>24703.945287</v>
+        <v>24703.729008</v>
       </c>
       <c r="G116" t="n">
-        <v>27008.030166</v>
+        <v>27007.538116</v>
       </c>
       <c r="H116" t="n">
-        <v>30462.725149</v>
+        <v>30461.575327</v>
       </c>
       <c r="I116" t="n">
-        <v>35835.051391</v>
+        <v>35831.564718</v>
       </c>
       <c r="J116" t="n">
         <v>12240.727751</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>34800.004007</v>
+        <v>34799.957938</v>
       </c>
       <c r="F117" t="n">
-        <v>41185.011782</v>
+        <v>41184.890513</v>
       </c>
       <c r="G117" t="n">
-        <v>48348.168597</v>
+        <v>48347.892149</v>
       </c>
       <c r="H117" t="n">
-        <v>55943.460747</v>
+        <v>55942.817349</v>
       </c>
       <c r="I117" t="n">
-        <v>65891.387561</v>
+        <v>65889.45013500001</v>
       </c>
       <c r="J117" t="n">
         <v>66425.133522</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>65563.714299</v>
+        <v>65563.686547</v>
       </c>
       <c r="F118" t="n">
-        <v>61494.857584</v>
+        <v>61494.785606</v>
       </c>
       <c r="G118" t="n">
-        <v>63691.02258</v>
+        <v>63690.849615</v>
       </c>
       <c r="H118" t="n">
-        <v>68501.948339</v>
+        <v>68501.52525799999</v>
       </c>
       <c r="I118" t="n">
-        <v>77545.753289</v>
+        <v>77544.42617399999</v>
       </c>
       <c r="J118" t="n">
         <v>85160.37323100001</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>13864.271081</v>
+        <v>13864.266747</v>
       </c>
       <c r="F119" t="n">
-        <v>15697.176186</v>
+        <v>15697.170151</v>
       </c>
       <c r="G119" t="n">
-        <v>19360.320164</v>
+        <v>19360.317718</v>
       </c>
       <c r="H119" t="n">
-        <v>23881.634823</v>
+        <v>23881.650549</v>
       </c>
       <c r="I119" t="n">
-        <v>29851.355141</v>
+        <v>29851.443474</v>
       </c>
       <c r="J119" t="n">
         <v>41926.542358</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9960.132135</v>
+        <v>9960.108463</v>
       </c>
       <c r="F120" t="n">
-        <v>9823.099029000001</v>
+        <v>9823.03853</v>
       </c>
       <c r="G120" t="n">
-        <v>10825.98628</v>
+        <v>10825.847353</v>
       </c>
       <c r="H120" t="n">
-        <v>12330.533003</v>
+        <v>12330.204683</v>
       </c>
       <c r="I120" t="n">
-        <v>14680.857464</v>
+        <v>14679.84858</v>
       </c>
       <c r="J120" t="n">
         <v>9333.466968000001</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>64609.465325</v>
+        <v>64609.485113</v>
       </c>
       <c r="F121" t="n">
-        <v>72250.064058</v>
+        <v>72250.158859</v>
       </c>
       <c r="G121" t="n">
-        <v>87750.639243</v>
+        <v>87750.94781300001</v>
       </c>
       <c r="H121" t="n">
-        <v>105477.453351</v>
+        <v>105478.313417</v>
       </c>
       <c r="I121" t="n">
-        <v>127624.973834</v>
+        <v>127627.73967</v>
       </c>
       <c r="J121" t="n">
         <v>196241.328434</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>523760.01313</v>
+        <v>523760.180345</v>
       </c>
       <c r="F122" t="n">
-        <v>519467.635437</v>
+        <v>519468.016697</v>
       </c>
       <c r="G122" t="n">
-        <v>578631.032356</v>
+        <v>578631.8066219999</v>
       </c>
       <c r="H122" t="n">
-        <v>669388.0955000001</v>
+        <v>669389.764329</v>
       </c>
       <c r="I122" t="n">
-        <v>812595.254576</v>
+        <v>812600.160505</v>
       </c>
       <c r="J122" t="n">
         <v>1155486.447486</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185975.977611</v>
+        <v>185995.201779</v>
       </c>
       <c r="F123" t="n">
-        <v>200713.007055</v>
+        <v>200762.624622</v>
       </c>
       <c r="G123" t="n">
-        <v>234866.375601</v>
+        <v>234976.51463</v>
       </c>
       <c r="H123" t="n">
-        <v>264500.559772</v>
+        <v>264737.495299</v>
       </c>
       <c r="I123" t="n">
-        <v>295605.80686</v>
+        <v>296238.190703</v>
       </c>
       <c r="J123" t="n">
         <v>41478.766526</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>500201.149155</v>
+        <v>500214.874847</v>
       </c>
       <c r="F124" t="n">
-        <v>539458.484274</v>
+        <v>539491.8057049999</v>
       </c>
       <c r="G124" t="n">
-        <v>620237.939295</v>
+        <v>620304.507109</v>
       </c>
       <c r="H124" t="n">
-        <v>688670.419801</v>
+        <v>688800.732014</v>
       </c>
       <c r="I124" t="n">
-        <v>759009.385643</v>
+        <v>759326.5066279999</v>
       </c>
       <c r="J124" t="n">
         <v>728778.430281</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>197086.179233</v>
+        <v>197053.229375</v>
       </c>
       <c r="F125" t="n">
-        <v>197224.653893</v>
+        <v>197141.714896</v>
       </c>
       <c r="G125" t="n">
-        <v>208449.24018</v>
+        <v>208272.533337</v>
       </c>
       <c r="H125" t="n">
-        <v>218119.461462</v>
+        <v>217752.213722</v>
       </c>
       <c r="I125" t="n">
-        <v>234726.467528</v>
+        <v>233776.9627</v>
       </c>
       <c r="J125" t="n">
         <v>706996.956631</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4885.180929</v>
+        <v>4885.16488</v>
       </c>
       <c r="F130" t="n">
-        <v>22362.416811</v>
+        <v>22362.180375</v>
       </c>
       <c r="G130" t="n">
-        <v>46496.695794</v>
+        <v>46495.359585</v>
       </c>
       <c r="H130" t="n">
-        <v>74506.958892</v>
+        <v>74500.66892500001</v>
       </c>
       <c r="I130" t="n">
-        <v>106528.841613</v>
+        <v>106490.136157</v>
       </c>
       <c r="J130" t="n">
         <v>3471957.954432</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.000694</v>
+        <v>0.00017</v>
       </c>
       <c r="F131" t="n">
-        <v>0.013296</v>
+        <v>0.003252</v>
       </c>
       <c r="G131" t="n">
-        <v>0.073724</v>
+        <v>0.018031</v>
       </c>
       <c r="H131" t="n">
-        <v>0.319949</v>
+        <v>0.078253</v>
       </c>
       <c r="I131" t="n">
-        <v>1.82731</v>
+        <v>0.446931</v>
       </c>
       <c r="J131" t="n">
         <v>113060.671576</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>80794.59246499999</v>
+        <v>80794.60698</v>
       </c>
       <c r="F132" t="n">
-        <v>337284.652605</v>
+        <v>337284.828351</v>
       </c>
       <c r="G132" t="n">
-        <v>620556.592373</v>
+        <v>620557.408752</v>
       </c>
       <c r="H132" t="n">
-        <v>878700.3201210001</v>
+        <v>878703.659474</v>
       </c>
       <c r="I132" t="n">
-        <v>1143156.856479</v>
+        <v>1143175.722733</v>
       </c>
       <c r="J132" t="n">
         <v>246767.453005</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>12208.88311</v>
+        <v>12208.885472</v>
       </c>
       <c r="F133" t="n">
-        <v>76093.096686</v>
+        <v>76093.136203</v>
       </c>
       <c r="G133" t="n">
-        <v>201219.70496</v>
+        <v>201219.936013</v>
       </c>
       <c r="H133" t="n">
-        <v>367079.027459</v>
+        <v>367080.116243</v>
       </c>
       <c r="I133" t="n">
-        <v>551042.030839</v>
+        <v>551048.832203</v>
       </c>
       <c r="J133" t="n">
         <v>321979.051208</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>23317.15496</v>
+        <v>23317.157999</v>
       </c>
       <c r="F134" t="n">
-        <v>90512.281773</v>
+        <v>90512.31948400001</v>
       </c>
       <c r="G134" t="n">
-        <v>160559.746257</v>
+        <v>160559.927994</v>
       </c>
       <c r="H134" t="n">
-        <v>227780.142996</v>
+        <v>227780.921407</v>
       </c>
       <c r="I134" t="n">
-        <v>301013.964014</v>
+        <v>301018.550972</v>
       </c>
       <c r="J134" t="n">
         <v>90096.136839</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8072.126319</v>
+        <v>8072.128005</v>
       </c>
       <c r="F135" t="n">
-        <v>42625.306927</v>
+        <v>42625.332837</v>
       </c>
       <c r="G135" t="n">
-        <v>100187.500362</v>
+        <v>100187.652185</v>
       </c>
       <c r="H135" t="n">
-        <v>172477.319595</v>
+        <v>172478.059945</v>
       </c>
       <c r="I135" t="n">
-        <v>256901.839976</v>
+        <v>256906.564427</v>
       </c>
       <c r="J135" t="n">
         <v>19039.26277</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1325.399467</v>
+        <v>1325.396263</v>
       </c>
       <c r="F136" t="n">
-        <v>5208.152773</v>
+        <v>5208.121689</v>
       </c>
       <c r="G136" t="n">
-        <v>8717.979393</v>
+        <v>8717.885059</v>
       </c>
       <c r="H136" t="n">
-        <v>11250.816228</v>
+        <v>11250.585205</v>
       </c>
       <c r="I136" t="n">
-        <v>14022.110549</v>
+        <v>14021.200915</v>
       </c>
       <c r="J136" t="n">
         <v>82291.763506</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10012.482808</v>
+        <v>10012.484637</v>
       </c>
       <c r="F137" t="n">
-        <v>43103.201462</v>
+        <v>43103.224004</v>
       </c>
       <c r="G137" t="n">
-        <v>78531.493103</v>
+        <v>78531.596873</v>
       </c>
       <c r="H137" t="n">
-        <v>110743.999267</v>
+        <v>110744.421929</v>
       </c>
       <c r="I137" t="n">
-        <v>143440.081111</v>
+        <v>143442.457488</v>
       </c>
       <c r="J137" t="n">
         <v>29558.019342</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>116.758428</v>
+        <v>116.757928</v>
       </c>
       <c r="F138" t="n">
-        <v>495.102263</v>
+        <v>495.095933</v>
       </c>
       <c r="G138" t="n">
-        <v>933.17565</v>
+        <v>933.1475380000001</v>
       </c>
       <c r="H138" t="n">
-        <v>1341.86447</v>
+        <v>1341.764666</v>
       </c>
       <c r="I138" t="n">
-        <v>1731.901134</v>
+        <v>1731.433217</v>
       </c>
       <c r="J138" t="n">
         <v>34482.218399</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>373.763595</v>
+        <v>373.763602</v>
       </c>
       <c r="F139" t="n">
-        <v>1676.97861</v>
+        <v>1676.978613</v>
       </c>
       <c r="G139" t="n">
-        <v>3446.69406</v>
+        <v>3446.693664</v>
       </c>
       <c r="H139" t="n">
-        <v>5487.640929</v>
+        <v>5487.638336</v>
       </c>
       <c r="I139" t="n">
-        <v>7816.245329</v>
+        <v>7816.229041</v>
       </c>
       <c r="J139" t="n">
         <v>14130.192689</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>518.810303</v>
+        <v>518.805576</v>
       </c>
       <c r="F140" t="n">
-        <v>2031.630494</v>
+        <v>2031.583894</v>
       </c>
       <c r="G140" t="n">
-        <v>3663.316017</v>
+        <v>3663.135866</v>
       </c>
       <c r="H140" t="n">
-        <v>5329.679316</v>
+        <v>5329.028409</v>
       </c>
       <c r="I140" t="n">
-        <v>7260.370037</v>
+        <v>7256.885162</v>
       </c>
       <c r="J140" t="n">
         <v>294533.296541</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1965.077935</v>
+        <v>1965.078293</v>
       </c>
       <c r="F141" t="n">
-        <v>9071.232773</v>
+        <v>9071.237477000001</v>
       </c>
       <c r="G141" t="n">
-        <v>18784.117392</v>
+        <v>18784.14129</v>
       </c>
       <c r="H141" t="n">
-        <v>29581.074188</v>
+        <v>29581.180513</v>
       </c>
       <c r="I141" t="n">
-        <v>41655.363986</v>
+        <v>41656.006184</v>
       </c>
       <c r="J141" t="n">
         <v>13671.624575</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5828.240188</v>
+        <v>5828.241396</v>
       </c>
       <c r="F142" t="n">
-        <v>41436.283918</v>
+        <v>41436.308279</v>
       </c>
       <c r="G142" t="n">
-        <v>136791.599802</v>
+        <v>136791.786037</v>
       </c>
       <c r="H142" t="n">
-        <v>299480.005461</v>
+        <v>299481.045564</v>
       </c>
       <c r="I142" t="n">
-        <v>510201.197961</v>
+        <v>510208.164909</v>
       </c>
       <c r="J142" t="n">
         <v>287673.452497</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>7288.90672</v>
+        <v>7288.909749</v>
       </c>
       <c r="F146" t="n">
-        <v>6929.117891</v>
+        <v>6929.126102</v>
       </c>
       <c r="G146" t="n">
-        <v>7190.397638</v>
+        <v>7190.416901</v>
       </c>
       <c r="H146" t="n">
-        <v>8057.560962</v>
+        <v>8057.607886</v>
       </c>
       <c r="I146" t="n">
-        <v>9557.912499</v>
+        <v>9558.058805999999</v>
       </c>
       <c r="J146" t="n">
         <v>3422.874599</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3036.541113</v>
+        <v>3036.538273</v>
       </c>
       <c r="F147" t="n">
-        <v>3322.4318</v>
+        <v>3322.423423</v>
       </c>
       <c r="G147" t="n">
-        <v>3802.588197</v>
+        <v>3802.568052</v>
       </c>
       <c r="H147" t="n">
-        <v>4424.569426</v>
+        <v>4424.52083</v>
       </c>
       <c r="I147" t="n">
-        <v>5263.041597</v>
+        <v>5262.891875</v>
       </c>
       <c r="J147" t="n">
         <v>15449.111745</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>303583.87911</v>
+        <v>303583.878923</v>
       </c>
       <c r="F148" t="n">
-        <v>350423.219573</v>
+        <v>350423.21974</v>
       </c>
       <c r="G148" t="n">
-        <v>434978.991079</v>
+        <v>434978.991961</v>
       </c>
       <c r="H148" t="n">
-        <v>540275.993323</v>
+        <v>540275.994995</v>
       </c>
       <c r="I148" t="n">
-        <v>665259.488545</v>
+        <v>665259.49196</v>
       </c>
       <c r="J148" t="n">
         <v>844843.0467459999</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>48871.466626</v>
+        <v>48871.556148</v>
       </c>
       <c r="F149" t="n">
-        <v>56538.211695</v>
+        <v>56538.456948</v>
       </c>
       <c r="G149" t="n">
-        <v>68264.49823300001</v>
+        <v>68265.090728</v>
       </c>
       <c r="H149" t="n">
-        <v>82995.17677799999</v>
+        <v>82996.672947</v>
       </c>
       <c r="I149" t="n">
-        <v>101102.703141</v>
+        <v>101107.504631</v>
       </c>
       <c r="J149" t="n">
         <v>177058.437652</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>395462.370639</v>
+        <v>395462.289581</v>
       </c>
       <c r="F150" t="n">
-        <v>448505.125064</v>
+        <v>448504.776768</v>
       </c>
       <c r="G150" t="n">
-        <v>535658.200575</v>
+        <v>535657.35769</v>
       </c>
       <c r="H150" t="n">
-        <v>631783.579813</v>
+        <v>631781.922055</v>
       </c>
       <c r="I150" t="n">
-        <v>731154.819692</v>
+        <v>731151.498772</v>
       </c>
       <c r="J150" t="n">
         <v>868272.925404</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>68672.202709</v>
+        <v>68672.762092</v>
       </c>
       <c r="F151" t="n">
-        <v>84040.52680399999</v>
+        <v>84042.237718</v>
       </c>
       <c r="G151" t="n">
-        <v>107130.928301</v>
+        <v>107135.337911</v>
       </c>
       <c r="H151" t="n">
-        <v>132488.91328</v>
+        <v>132499.972052</v>
       </c>
       <c r="I151" t="n">
-        <v>158973.725683</v>
+        <v>159007.151289</v>
       </c>
       <c r="J151" t="n">
         <v>497154.499599</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>232293.885989</v>
+        <v>232294.9959</v>
       </c>
       <c r="F152" t="n">
-        <v>288729.029845</v>
+        <v>288732.47579</v>
       </c>
       <c r="G152" t="n">
-        <v>350368.108293</v>
+        <v>350376.542786</v>
       </c>
       <c r="H152" t="n">
-        <v>408341.683909</v>
+        <v>408361.625495</v>
       </c>
       <c r="I152" t="n">
-        <v>464477.622827</v>
+        <v>464535.026192</v>
       </c>
       <c r="J152" t="n">
         <v>1050899.664422</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>294581.658381</v>
+        <v>294580.239938</v>
       </c>
       <c r="F153" t="n">
-        <v>342169.646006</v>
+        <v>342165.411851</v>
       </c>
       <c r="G153" t="n">
-        <v>426071.543544</v>
+        <v>426060.925655</v>
       </c>
       <c r="H153" t="n">
-        <v>532010.48612</v>
+        <v>531984.096374</v>
       </c>
       <c r="I153" t="n">
-        <v>656691.92547</v>
+        <v>656611.5368229999</v>
       </c>
       <c r="J153" t="n">
         <v>119194.043674</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>119987.171655</v>
+        <v>119986.912341</v>
       </c>
       <c r="F154" t="n">
-        <v>145487.10361</v>
+        <v>145486.283948</v>
       </c>
       <c r="G154" t="n">
-        <v>174739.570515</v>
+        <v>174737.594692</v>
       </c>
       <c r="H154" t="n">
-        <v>200238.460354</v>
+        <v>200234.01133</v>
       </c>
       <c r="I154" t="n">
-        <v>221609.422864</v>
+        <v>221597.501969</v>
       </c>
       <c r="J154" t="n">
         <v>161323.787845</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>190235.593949</v>
+        <v>190206.107395</v>
       </c>
       <c r="F155" t="n">
-        <v>187524.867235</v>
+        <v>187456.334512</v>
       </c>
       <c r="G155" t="n">
-        <v>222193.623876</v>
+        <v>222039.38345</v>
       </c>
       <c r="H155" t="n">
-        <v>277626.015094</v>
+        <v>277261.128942</v>
       </c>
       <c r="I155" t="n">
-        <v>350246.877033</v>
+        <v>349182.314742</v>
       </c>
       <c r="J155" t="n">
         <v>291685.03317</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>372784.724251</v>
+        <v>372903.525426</v>
       </c>
       <c r="F156" t="n">
-        <v>350431.243892</v>
+        <v>350707.858729</v>
       </c>
       <c r="G156" t="n">
-        <v>394401.508754</v>
+        <v>395017.468616</v>
       </c>
       <c r="H156" t="n">
-        <v>464654.913714</v>
+        <v>466079.817052</v>
       </c>
       <c r="I156" t="n">
-        <v>556484.5610409999</v>
+        <v>560564.966554</v>
       </c>
       <c r="J156" t="n">
         <v>1530234.461171</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4247.954829</v>
+        <v>4250.376621</v>
       </c>
       <c r="F157" t="n">
-        <v>5044.569081</v>
+        <v>5051.295919</v>
       </c>
       <c r="G157" t="n">
-        <v>6927.716175</v>
+        <v>6945.135767</v>
       </c>
       <c r="H157" t="n">
-        <v>9179.876138</v>
+        <v>9223.939407</v>
       </c>
       <c r="I157" t="n">
-        <v>11467.564585</v>
+        <v>11597.397321</v>
       </c>
       <c r="J157" t="n">
         <v>40262.071193</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>207034.299159</v>
+        <v>207043.038771</v>
       </c>
       <c r="F158" t="n">
-        <v>171200.411817</v>
+        <v>171222.660188</v>
       </c>
       <c r="G158" t="n">
-        <v>168693.270445</v>
+        <v>168744.672847</v>
       </c>
       <c r="H158" t="n">
-        <v>180328.538307</v>
+        <v>180449.758171</v>
       </c>
       <c r="I158" t="n">
-        <v>201746.975819</v>
+        <v>202103.41378</v>
       </c>
       <c r="J158" t="n">
         <v>330423.469109</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1805.615362</v>
+        <v>1806.41521</v>
       </c>
       <c r="F159" t="n">
-        <v>1624.807381</v>
+        <v>1626.608883</v>
       </c>
       <c r="G159" t="n">
-        <v>1777.30992</v>
+        <v>1781.233137</v>
       </c>
       <c r="H159" t="n">
-        <v>2040.5477</v>
+        <v>2049.429848</v>
       </c>
       <c r="I159" t="n">
-        <v>2402.846449</v>
+        <v>2427.808306</v>
       </c>
       <c r="J159" t="n">
         <v>7856.071614</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>435266.00045</v>
+        <v>435164.724577</v>
       </c>
       <c r="F160" t="n">
-        <v>428299.595327</v>
+        <v>428060.736502</v>
       </c>
       <c r="G160" t="n">
-        <v>497252.93016</v>
+        <v>496718.465512</v>
       </c>
       <c r="H160" t="n">
-        <v>598133.846823</v>
+        <v>596899.664356</v>
       </c>
       <c r="I160" t="n">
-        <v>725777.066289</v>
+        <v>722249.9905130001</v>
       </c>
       <c r="J160" t="n">
         <v>325046.851298</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>11.860741</v>
+        <v>12.109616</v>
       </c>
       <c r="F162" t="n">
-        <v>13.530383</v>
+        <v>13.953696</v>
       </c>
       <c r="G162" t="n">
-        <v>18.240869</v>
+        <v>18.927055</v>
       </c>
       <c r="H162" t="n">
-        <v>30.417287</v>
+        <v>31.69621</v>
       </c>
       <c r="I162" t="n">
-        <v>74.44916600000001</v>
+        <v>77.81805</v>
       </c>
       <c r="J162" t="n">
         <v>18474.034955</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4221.925644</v>
+        <v>4221.938869</v>
       </c>
       <c r="F163" t="n">
-        <v>4876.071236</v>
+        <v>4876.115322</v>
       </c>
       <c r="G163" t="n">
-        <v>6581.271686</v>
+        <v>6581.407374</v>
       </c>
       <c r="H163" t="n">
-        <v>8538.267209</v>
+        <v>8538.650787</v>
       </c>
       <c r="I163" t="n">
-        <v>10738.444703</v>
+        <v>10739.714089</v>
       </c>
       <c r="J163" t="n">
         <v>22043.599371</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>129333.048215</v>
+        <v>129332.242643</v>
       </c>
       <c r="F164" t="n">
-        <v>163759.759615</v>
+        <v>163757.288447</v>
       </c>
       <c r="G164" t="n">
-        <v>234795.306437</v>
+        <v>234788.410407</v>
       </c>
       <c r="H164" t="n">
-        <v>324430.377347</v>
+        <v>324411.705302</v>
       </c>
       <c r="I164" t="n">
-        <v>434772.956147</v>
+        <v>434711.488913</v>
       </c>
       <c r="J164" t="n">
         <v>247973.771172</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>109769.705189</v>
+        <v>109768.950674</v>
       </c>
       <c r="F165" t="n">
-        <v>121665.237517</v>
+        <v>121663.181017</v>
       </c>
       <c r="G165" t="n">
-        <v>137160.365792</v>
+        <v>137155.756527</v>
       </c>
       <c r="H165" t="n">
-        <v>156441.618179</v>
+        <v>156431.128883</v>
       </c>
       <c r="I165" t="n">
-        <v>183410.699024</v>
+        <v>183380.061115</v>
       </c>
       <c r="J165" t="n">
         <v>68043.660909</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>468745.238966</v>
+        <v>468741.653127</v>
       </c>
       <c r="F166" t="n">
-        <v>491435.119025</v>
+        <v>491425.831229</v>
       </c>
       <c r="G166" t="n">
-        <v>580834.3967480001</v>
+        <v>580812.597188</v>
       </c>
       <c r="H166" t="n">
-        <v>690738.894183</v>
+        <v>690687.2474390001</v>
       </c>
       <c r="I166" t="n">
-        <v>821884.044444</v>
+        <v>821731.024095</v>
       </c>
       <c r="J166" t="n">
         <v>215342.506898</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>75551.020556</v>
+        <v>75555.286752</v>
       </c>
       <c r="F167" t="n">
-        <v>75923.409248</v>
+        <v>75934.242098</v>
       </c>
       <c r="G167" t="n">
-        <v>88322.16876499999</v>
+        <v>88347.637688</v>
       </c>
       <c r="H167" t="n">
-        <v>107514.037929</v>
+        <v>107576.553231</v>
       </c>
       <c r="I167" t="n">
-        <v>136180.787371</v>
+        <v>136377.277468</v>
       </c>
       <c r="J167" t="n">
         <v>1365357.044922</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1275.084763</v>
+        <v>1275.094149</v>
       </c>
       <c r="F168" t="n">
-        <v>1406.533603</v>
+        <v>1406.561012</v>
       </c>
       <c r="G168" t="n">
-        <v>1750.333417</v>
+        <v>1750.404916</v>
       </c>
       <c r="H168" t="n">
-        <v>2189.060309</v>
+        <v>2189.24557</v>
       </c>
       <c r="I168" t="n">
-        <v>2755.515679</v>
+        <v>2756.111729</v>
       </c>
       <c r="J168" t="n">
         <v>7454.10202</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>791808.041491</v>
+        <v>791804.340933</v>
       </c>
       <c r="F169" t="n">
-        <v>861549.161692</v>
+        <v>861539.407513</v>
       </c>
       <c r="G169" t="n">
-        <v>1055354.050737</v>
+        <v>1055330.700894</v>
       </c>
       <c r="H169" t="n">
-        <v>1331373.99224</v>
+        <v>1331316.243216</v>
       </c>
       <c r="I169" t="n">
-        <v>1726428.415726</v>
+        <v>1726245.228175</v>
       </c>
       <c r="J169" t="n">
         <v>1375433.347555</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>35637.640964</v>
+        <v>35637.628107</v>
       </c>
       <c r="F170" t="n">
-        <v>47138.731034</v>
+        <v>47138.743346</v>
       </c>
       <c r="G170" t="n">
-        <v>66504.114384</v>
+        <v>66504.26916900001</v>
       </c>
       <c r="H170" t="n">
-        <v>88548.38103999999</v>
+        <v>88549.001114</v>
       </c>
       <c r="I170" t="n">
-        <v>114046.189119</v>
+        <v>114048.614442</v>
       </c>
       <c r="J170" t="n">
         <v>174234.670301</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>76104.49450299999</v>
+        <v>76105.742941</v>
       </c>
       <c r="F171" t="n">
-        <v>79838.189829</v>
+        <v>79841.590482</v>
       </c>
       <c r="G171" t="n">
-        <v>94693.549031</v>
+        <v>94701.879116</v>
       </c>
       <c r="H171" t="n">
-        <v>112819.339065</v>
+        <v>112839.669194</v>
       </c>
       <c r="I171" t="n">
-        <v>135367.739221</v>
+        <v>135429.422851</v>
       </c>
       <c r="J171" t="n">
         <v>533684.1322540001</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>14733.550389</v>
+        <v>14738.09284</v>
       </c>
       <c r="F172" t="n">
-        <v>14637.32089</v>
+        <v>14648.634839</v>
       </c>
       <c r="G172" t="n">
-        <v>15969.885411</v>
+        <v>15994.310266</v>
       </c>
       <c r="H172" t="n">
-        <v>17974.629515</v>
+        <v>18028.01643</v>
       </c>
       <c r="I172" t="n">
-        <v>22207.050938</v>
+        <v>22357.807157</v>
       </c>
       <c r="J172" t="n">
         <v>857051.714931</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2837.881451</v>
+        <v>2837.87201</v>
       </c>
       <c r="F173" t="n">
-        <v>3601.236529</v>
+        <v>3601.209139</v>
       </c>
       <c r="G173" t="n">
-        <v>4943.091557</v>
+        <v>4943.021701</v>
       </c>
       <c r="H173" t="n">
-        <v>6483.926974</v>
+        <v>6483.752639</v>
       </c>
       <c r="I173" t="n">
-        <v>8382.785911999999</v>
+        <v>8382.24423</v>
       </c>
       <c r="J173" t="n">
         <v>8617.89791</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1004176.184318</v>
+        <v>1004174.93541</v>
       </c>
       <c r="F174" t="n">
-        <v>1003531.773082</v>
+        <v>1003529.106012</v>
       </c>
       <c r="G174" t="n">
-        <v>1141405.49316</v>
+        <v>1141400.243731</v>
       </c>
       <c r="H174" t="n">
-        <v>1335925.142984</v>
+        <v>1335914.483321</v>
       </c>
       <c r="I174" t="n">
-        <v>1601589.547794</v>
+        <v>1601562.183639</v>
       </c>
       <c r="J174" t="n">
         <v>2031363.680671</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5860.198472</v>
+        <v>5860.165456</v>
       </c>
       <c r="F175" t="n">
-        <v>9045.776102</v>
+        <v>9045.655363</v>
       </c>
       <c r="G175" t="n">
-        <v>15154.30182</v>
+        <v>15153.91598</v>
       </c>
       <c r="H175" t="n">
-        <v>23632.388099</v>
+        <v>23631.22801</v>
       </c>
       <c r="I175" t="n">
-        <v>35105.02507</v>
+        <v>35100.851857</v>
       </c>
       <c r="J175" t="n">
         <v>27503.234265</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>501.467063</v>
+        <v>501.473728</v>
       </c>
       <c r="F176" t="n">
-        <v>474.419925</v>
+        <v>474.43599</v>
       </c>
       <c r="G176" t="n">
-        <v>524.732429</v>
+        <v>524.768713</v>
       </c>
       <c r="H176" t="n">
-        <v>603.163474</v>
+        <v>603.248471</v>
       </c>
       <c r="I176" t="n">
-        <v>713.551919</v>
+        <v>713.806107</v>
       </c>
       <c r="J176" t="n">
         <v>2388.750204</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>518198.358303</v>
+        <v>518198.150728</v>
       </c>
       <c r="F177" t="n">
-        <v>699607.543498</v>
+        <v>699607.790716</v>
       </c>
       <c r="G177" t="n">
-        <v>998322.8035339999</v>
+        <v>998325.68168</v>
       </c>
       <c r="H177" t="n">
-        <v>1314418.832557</v>
+        <v>1314430.154307</v>
       </c>
       <c r="I177" t="n">
-        <v>1637846.77</v>
+        <v>1637888.904687</v>
       </c>
       <c r="J177" t="n">
         <v>2433277.319424</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1258.722025</v>
+        <v>1258.735948</v>
       </c>
       <c r="F178" t="n">
-        <v>1463.752235</v>
+        <v>1463.794884</v>
       </c>
       <c r="G178" t="n">
-        <v>1867.952928</v>
+        <v>1868.066059</v>
       </c>
       <c r="H178" t="n">
-        <v>2374.58435</v>
+        <v>2374.879849</v>
       </c>
       <c r="I178" t="n">
-        <v>3027.61475</v>
+        <v>3028.570179</v>
       </c>
       <c r="J178" t="n">
         <v>10077.813378</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>871.391946</v>
+        <v>871.40107</v>
       </c>
       <c r="F179" t="n">
-        <v>890.560745</v>
+        <v>890.5850840000001</v>
       </c>
       <c r="G179" t="n">
-        <v>1056.456975</v>
+        <v>1056.517215</v>
       </c>
       <c r="H179" t="n">
-        <v>1262.753772</v>
+        <v>1262.902539</v>
       </c>
       <c r="I179" t="n">
-        <v>1523.708376</v>
+        <v>1524.166578</v>
       </c>
       <c r="J179" t="n">
         <v>4699.385505</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-0</v>
+        <v>-6e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="G181" t="n">
         <v>-1e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>-4e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="I181" t="n">
-        <v>4e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="J181" t="n">
-        <v>-6e-06</v>
+        <v>-7e-06</v>
       </c>
       <c r="K181" t="n">
-        <v>-5e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="L181" t="n">
         <v>2e-06</v>
       </c>
       <c r="M181" t="n">
-        <v>-5e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="N181" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="O181" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="Q181" t="n">
         <v>4e-06</v>
-      </c>
-      <c r="O181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>1e-06</v>
       </c>
       <c r="R181" t="n">
         <v>1e-06</v>
       </c>
       <c r="S181" t="n">
-        <v>3e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="T181" t="n">
-        <v>1.2e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="U181" t="n">
         <v>2e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>5e-06</v>
+        <v>6e-06</v>
       </c>
     </row>
   </sheetData>
